--- a/files/九龙-启德-天泷.xlsx
+++ b/files/九龙-启德-天泷.xlsx
@@ -8,14 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座 销控表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座 销控表" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座 销控表" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6座 销控表" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7座 销控表" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8座 销控表" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harbour Mansion 销控表" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -118,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -183,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -199,51 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -765,7 +619,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -811,7 +665,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -957,7 +811,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1103,7 +957,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1249,7 +1103,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1395,7 +1249,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1491,7 +1345,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1537,7 +1391,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1633,7 +1487,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1679,7 +1533,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1775,7 +1629,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -1821,7 +1675,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1867,7 +1721,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1913,7 +1767,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -1959,7 +1813,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2005,7 +1859,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2051,7 +1905,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-26</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2097,7 +1951,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2193,7 +2047,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2239,7 +2093,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2285,7 +2139,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2331,7 +2185,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2377,7 +2231,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2423,7 +2277,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2469,7 +2323,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-05</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2515,7 +2369,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2561,7 +2415,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -2607,7 +2461,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2653,7 +2507,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -2749,7 +2603,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -2795,7 +2649,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -2841,7 +2695,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -2887,7 +2741,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2933,7 +2787,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -2979,7 +2833,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3025,7 +2879,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3071,7 +2925,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3217,7 +3071,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -3313,7 +3167,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -3359,7 +3213,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3405,7 +3259,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -3451,7 +3305,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-28</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3497,7 +3351,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3543,7 +3397,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3589,7 +3443,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -3635,7 +3489,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -3681,7 +3535,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -3727,7 +3581,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -3773,7 +3627,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -3819,7 +3673,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -3865,7 +3719,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -3911,7 +3765,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -3957,7 +3811,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -4003,7 +3857,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -4049,7 +3903,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -4095,7 +3949,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -4141,7 +3995,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -4187,7 +4041,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -4233,7 +4087,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -4279,7 +4133,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -4325,7 +4179,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -4371,7 +4225,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4417,7 +4271,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -4463,7 +4317,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -4509,7 +4363,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -4855,7 +4709,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -4951,7 +4805,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -5047,7 +4901,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -5143,7 +4997,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -5239,7 +5093,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -5335,7 +5189,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -5381,7 +5235,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -5427,7 +5281,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -5523,7 +5377,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -5569,7 +5423,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -5615,7 +5469,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -5661,7 +5515,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -5707,7 +5561,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -5753,7 +5607,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -5799,7 +5653,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -5845,7 +5699,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-30</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -5891,7 +5745,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -5937,7 +5791,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -5983,7 +5837,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -6029,7 +5883,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -6075,7 +5929,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -6121,7 +5975,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -6167,7 +6021,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-05-18</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -6259,7 +6113,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -6305,7 +6159,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -6351,7 +6205,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -6397,7 +6251,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -6443,7 +6297,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -6489,7 +6343,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -6535,7 +6389,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -6581,7 +6435,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-07-19</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -6627,7 +6481,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -6673,7 +6527,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -6719,7 +6573,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -6765,7 +6619,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -6811,7 +6665,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -6857,7 +6711,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -6903,7 +6757,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -6949,7 +6803,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -6995,7 +6849,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -7041,7 +6895,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -7087,7 +6941,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -7133,7 +6987,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -7279,7 +7133,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -8225,7 +8079,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -8271,7 +8125,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -8417,7 +8271,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -8613,7 +8467,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -8809,7 +8663,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -8855,7 +8709,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -9001,7 +8855,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -9047,7 +8901,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -9193,7 +9047,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-28</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -9239,7 +9093,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-28</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -9385,7 +9239,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -9431,7 +9285,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -9577,7 +9431,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -9623,7 +9477,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -9769,7 +9623,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -9815,7 +9669,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -9961,7 +9815,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -10007,7 +9861,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -10153,7 +10007,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -10199,7 +10053,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -10345,7 +10199,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -10391,7 +10245,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -10537,7 +10391,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -10583,7 +10437,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -10729,7 +10583,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -10775,7 +10629,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -10921,7 +10775,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -10967,7 +10821,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -11113,7 +10967,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -11159,7 +11013,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -11305,7 +11159,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -11351,7 +11205,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -11497,7 +11351,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -11543,7 +11397,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -11689,7 +11543,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-15</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -11735,7 +11589,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-15</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -11881,7 +11735,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -11927,7 +11781,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -12073,7 +11927,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -12119,7 +11973,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -12265,7 +12119,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -12311,7 +12165,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -12457,7 +12311,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -12503,7 +12357,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-15</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -13045,7 +12899,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -13141,7 +12995,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -13187,7 +13041,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -13233,7 +13087,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -13279,7 +13133,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -13421,7 +13275,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -13467,7 +13321,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -13513,7 +13367,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -13559,7 +13413,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -13605,7 +13459,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -13651,7 +13505,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -13697,7 +13551,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -13743,7 +13597,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -13789,7 +13643,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -13835,7 +13689,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -13881,7 +13735,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -13927,7 +13781,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -13973,7 +13827,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -14019,7 +13873,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -14065,7 +13919,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -14111,7 +13965,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -14157,7 +14011,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -14203,7 +14057,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="H287" s="5" t="n">
@@ -14249,7 +14103,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -14295,7 +14149,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -14341,7 +14195,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -14387,7 +14241,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -14433,7 +14287,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -14479,7 +14333,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -14525,7 +14379,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -14571,7 +14425,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -14617,7 +14471,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -14663,7 +14517,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H297" s="5" t="n">
@@ -14709,7 +14563,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -14755,7 +14609,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -14801,7 +14655,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -14847,7 +14701,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H301" s="5" t="n">
@@ -14893,7 +14747,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -14939,7 +14793,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -14985,7 +14839,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -15031,7 +14885,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
@@ -15077,7 +14931,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -15123,7 +14977,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
@@ -16419,7 +16273,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -16465,7 +16319,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -16661,7 +16515,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H338" s="5" t="n">
@@ -16807,7 +16661,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -16853,7 +16707,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="H342" s="5" t="n">
@@ -17049,7 +16903,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
@@ -17195,7 +17049,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -17241,7 +17095,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H350" s="5" t="n">
@@ -17387,7 +17241,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="H353" s="5" t="n">
@@ -17433,7 +17287,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="H354" s="5" t="n">
@@ -17579,7 +17433,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H357" s="5" t="n">
@@ -17625,7 +17479,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="H358" s="5" t="n">
@@ -17771,7 +17625,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
@@ -17817,7 +17671,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="H362" s="5" t="n">
@@ -17963,7 +17817,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="H365" s="5" t="n">
@@ -18009,7 +17863,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="H366" s="5" t="n">
@@ -18355,7 +18209,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H373" s="5" t="n">
@@ -18401,7 +18255,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H374" s="5" t="n">
@@ -18547,7 +18401,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="H377" s="5" t="n">
@@ -18593,7 +18447,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H378" s="5" t="n">
@@ -18739,7 +18593,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="H381" s="5" t="n">
@@ -18785,7 +18639,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="H382" s="5" t="n">
@@ -18931,7 +18785,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="H385" s="5" t="n">
@@ -18977,7 +18831,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="H386" s="5" t="n">
@@ -19123,7 +18977,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="H389" s="5" t="n">
@@ -19169,7 +19023,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="H390" s="5" t="n">
@@ -19315,7 +19169,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="H393" s="5" t="n">
@@ -19361,7 +19215,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="H394" s="5" t="n">
@@ -19507,7 +19361,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="H397" s="5" t="n">
@@ -19553,7 +19407,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="H398" s="5" t="n">
@@ -19699,7 +19553,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="H401" s="5" t="n">
@@ -19745,7 +19599,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="H402" s="5" t="n">
@@ -19891,7 +19745,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H405" s="5" t="n">
@@ -19937,7 +19791,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="H406" s="5" t="n">
@@ -20083,7 +19937,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="H409" s="5" t="n">
@@ -20129,7 +19983,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="H410" s="5" t="n">
@@ -20325,7 +20179,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="H414" s="5" t="n">
@@ -20521,7 +20375,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="H418" s="5" t="n">
@@ -21017,7 +20871,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="H428" s="5" t="n">
@@ -21063,7 +20917,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="H429" s="5" t="n">
@@ -21109,7 +20963,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="H430" s="5" t="n">
@@ -21155,7 +21009,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="H431" s="5" t="n">
@@ -21201,7 +21055,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="H432" s="5" t="n">
@@ -21247,7 +21101,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H433" s="5" t="n">
@@ -21293,7 +21147,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H434" s="5" t="n">
@@ -21339,7 +21193,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="H435" s="5" t="n">
@@ -21385,7 +21239,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="H436" s="5" t="n">
@@ -21431,7 +21285,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="H437" s="5" t="n">
@@ -21477,7 +21331,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="H438" s="5" t="n">
@@ -21523,7 +21377,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="H439" s="5" t="n">
@@ -21569,7 +21423,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="H440" s="5" t="n">
@@ -21615,7 +21469,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H441" s="5" t="n">
@@ -21661,7 +21515,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="H442" s="5" t="n">
@@ -21707,7 +21561,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="H443" s="5" t="n">
@@ -21753,7 +21607,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="H444" s="5" t="n">
@@ -21799,7 +21653,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="H445" s="5" t="n">
@@ -21845,7 +21699,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="H446" s="5" t="n">
@@ -21891,7 +21745,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="H447" s="5" t="n">
@@ -21937,7 +21791,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="H448" s="5" t="n">
@@ -21983,7 +21837,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="H449" s="5" t="n">
@@ -22029,7 +21883,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="H450" s="5" t="n">
@@ -22075,7 +21929,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="H451" s="5" t="n">
@@ -22121,7 +21975,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="H452" s="5" t="n">
@@ -22167,7 +22021,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="H453" s="5" t="n">
@@ -22213,7 +22067,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="H454" s="5" t="n">
@@ -22259,7 +22113,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="H455" s="5" t="n">
@@ -22305,7 +22159,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="H456" s="5" t="n">
@@ -22351,7 +22205,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="H457" s="5" t="n">
@@ -22397,7 +22251,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="H458" s="5" t="n">
@@ -22443,7 +22297,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H459" s="5" t="n">
@@ -22489,7 +22343,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="H460" s="5" t="n">
@@ -22535,7 +22389,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="H461" s="5" t="n">
@@ -22581,7 +22435,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="H462" s="5" t="n">
@@ -22627,7 +22481,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H463" s="5" t="n">
@@ -22673,7 +22527,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="H464" s="5" t="n">
@@ -22710,7 +22564,7 @@
         </is>
       </c>
       <c r="E465" s="4" t="n">
-        <v>1173</v>
+        <v>1076</v>
       </c>
       <c r="F465" s="3" t="inlineStr">
         <is>
@@ -22719,14 +22573,14 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H465" s="5" t="n">
         <v>40580000</v>
       </c>
       <c r="I465" s="5" t="n">
-        <v>34595</v>
+        <v>37714</v>
       </c>
       <c r="J465" s="3" t="inlineStr">
         <is>
@@ -22765,7 +22619,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="H466" s="5" t="n">
@@ -22911,7 +22765,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="H469" s="5" t="n">
@@ -23857,7 +23711,7 @@
       </c>
       <c r="G488" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="H488" s="5" t="n">
@@ -24103,7 +23957,7 @@
       </c>
       <c r="G493" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H493" s="5" t="n">
@@ -24249,7 +24103,7 @@
       </c>
       <c r="G496" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="H496" s="5" t="n">
@@ -24495,7 +24349,7 @@
       </c>
       <c r="G501" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="H501" s="5" t="n">
@@ -24841,7 +24695,7 @@
       </c>
       <c r="G508" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="H508" s="5" t="n">
@@ -24887,7 +24741,7 @@
       </c>
       <c r="G509" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H509" s="5" t="n">
@@ -25033,7 +24887,7 @@
       </c>
       <c r="G512" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="H512" s="5" t="n">
@@ -25079,7 +24933,7 @@
       </c>
       <c r="G513" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-28</t>
         </is>
       </c>
       <c r="H513" s="5" t="n">
@@ -25225,7 +25079,7 @@
       </c>
       <c r="G516" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="H516" s="5" t="n">
@@ -25271,7 +25125,7 @@
       </c>
       <c r="G517" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="H517" s="5" t="n">
@@ -25417,7 +25271,7 @@
       </c>
       <c r="G520" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="H520" s="5" t="n">
@@ -25613,7 +25467,7 @@
       </c>
       <c r="G524" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="H524" s="5" t="n">
@@ -25809,7 +25663,7 @@
       </c>
       <c r="G528" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="H528" s="5" t="n">
@@ -25855,7 +25709,7 @@
       </c>
       <c r="G529" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="H529" s="5" t="n">
@@ -26201,7 +26055,7 @@
       </c>
       <c r="G536" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H536" s="5" t="n">
@@ -26247,7 +26101,7 @@
       </c>
       <c r="G537" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H537" s="5" t="n">
@@ -26393,7 +26247,7 @@
       </c>
       <c r="G540" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="H540" s="5" t="n">
@@ -26439,7 +26293,7 @@
       </c>
       <c r="G541" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H541" s="5" t="n">
@@ -26585,7 +26439,7 @@
       </c>
       <c r="G544" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H544" s="5" t="n">
@@ -26631,7 +26485,7 @@
       </c>
       <c r="G545" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H545" s="5" t="n">
@@ -26823,7 +26677,7 @@
       </c>
       <c r="G549" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="H549" s="5" t="n">
@@ -27019,7 +26873,7 @@
       </c>
       <c r="G553" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="H553" s="5" t="n">
@@ -27465,7 +27319,7 @@
       </c>
       <c r="G562" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="H562" s="5" t="n">
@@ -27511,7 +27365,7 @@
       </c>
       <c r="G563" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-02</t>
         </is>
       </c>
       <c r="H563" s="5" t="n">
@@ -27557,7 +27411,7 @@
       </c>
       <c r="G564" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="H564" s="5" t="n">
@@ -27603,7 +27457,7 @@
       </c>
       <c r="G565" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-07-31</t>
         </is>
       </c>
       <c r="H565" s="5" t="n">
@@ -27649,7 +27503,7 @@
       </c>
       <c r="G566" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-07-17</t>
         </is>
       </c>
       <c r="H566" s="5" t="n">
@@ -27695,7 +27549,7 @@
       </c>
       <c r="G567" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-07-17</t>
         </is>
       </c>
       <c r="H567" s="5" t="n">
@@ -27741,7 +27595,7 @@
       </c>
       <c r="G568" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-07-17</t>
         </is>
       </c>
       <c r="H568" s="5" t="n">
@@ -27763,6812 +27617,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>天泷 - 1座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>82 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>5 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>65 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>10 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 1942呎 (4+房)
-$11,215万
-$57,750/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>C | 635呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 1428呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 1258呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 590呎 (3房)
-$1,617万
-$27,399/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 1428呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 1258呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 590呎 (3房)
-$1,568万
-$26,576/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 1428呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 1258呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 590呎 (3房)
-$1,588万
-$26,907/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>A | 1428呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>B | 1258呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 590呎 (3房)
-$1,540万
-$26,099/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 1339呎 (4+房)
-$6,740万
-$50,336/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 1258呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 590呎 (3房)
-$1,575万
-$26,692/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 1339呎 (4+房)
-$6,665万
-$49,776/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>B | 1258呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 590呎 (3房)
-$1,568万
-$26,584/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 1339呎 (4+房)
-$6,007万
-$44,862/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>B | 1258呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 590呎 (3房)
-$1,562万
-$26,476/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 1339呎 (4+房)
-$6,453万
-$48,193/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 1171呎 (4+房)
-$5,285万
-$45,132/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 590呎 (3房)
-$1,509万
-$25,577/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 1428呎 (4+房)
-$5,860万
-$41,036/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 1171呎 (4+房)
-$4,868万
-$41,571/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 590呎 (3房)
-$1,497万
-$25,369/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 1339呎 (4+房)
-$5,810万
-$43,391/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>B | 1258呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 590呎 (3房)
-$1,537万
-$26,046/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 1339呎 (4+房)
-$6,161万
-$46,012/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 1171呎 (4+房)
-$4,900万
-$41,845/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 590呎 (3房)
-$1,491万
-$25,264/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 1428呎 (4+房)
-$5,733万
-$40,146/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 1171呎 (4+房)
-$4,756万
-$40,615/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 590呎 (3房)
-$1,524万
-$25,831/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 1339呎 (3房)
-$5,832万
-$43,555/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 1171呎 (4+房)
-$4,719万
-$40,299/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 590呎 (3房)
-$1,465万
-$24,825/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 1339呎 (4+房)
-$5,976万
-$44,630/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="inlineStr">
-        <is>
-          <t>B | 1258呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 590呎 (3房)
-$1,511万
-$25,615/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 1428呎 (4+房)
-$5,633万
-$39,447/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 1171呎 (4+房)
-$4,568万
-$39,009/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 590呎 (3房)
-$1,486万
-$25,185/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 1339呎 (4+房)
-$5,550万
-$41,449/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 1171呎 (4+房)
-$4,502万
-$38,446/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>C | 590呎 (3房)
-$1,461万
-$24,763/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 1428呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 1258呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>C | 590呎 (3房)
-$1,405万
-$23,814/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 1339呎 (4+房)
-$5,657万
-$42,248/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="19" t="inlineStr">
-        <is>
-          <t>B | 1258呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>C | 590呎 (3房)
-$1,440万
-$24,410/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 1428呎 (4+房)
-$5,614万
-$39,314/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>B | 1171呎 (4+房)
-$4,763万
-$40,675/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>C | 590呎 (3房)
-$1,422万
-$24,108/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A | 1339呎 (4+房)
-$5,468万
-$40,833/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>B | 1171呎 (4+房)
-$4,711万
-$40,231/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>C | 590呎 (3房)
-$1,416万
-$24,001/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>A | 1339呎 (4+房)
-$5,558万
-$41,509/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>B | 1171呎 (4+房)
-$4,510万
-$38,514/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>C | 590呎 (3房)
-$1,410万
-$23,893/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>A | 1339呎 (4+房)
-$5,546万
-$41,419/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>B | 1171呎 (4+房)
-$4,493万
-$38,369/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>C | 590呎 (3房)
-$1,407万
-$23,839/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 1339呎 (4+房)
-$5,365万
-$40,067/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>B | 1171呎 (4+房)
-$4,557万
-$38,915/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>C | 590呎 (3房)
-$1,361万
-$23,072/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>A | 1339呎 (4+房)
-$5,432万
-$40,568/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>B | 1171呎 (4+房)
-$4,408万
-$37,643/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D30" s="16" t="inlineStr">
-        <is>
-          <t>C | 590呎 (3房)
-$1,397万
-$23,678/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>A | 1339呎 (4+房)
-$5,393万
-$40,275/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>B | 1171呎 (4+房)
-$4,379万
-$37,395/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D31" s="16" t="inlineStr">
-        <is>
-          <t>C | 590呎 (3房)
-$1,349万
-$22,864/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>A | 1339呎 (4+房)
-$5,327万
-$39,783/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>B | 1171呎 (4+房)
-$4,460万
-$38,087/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D32" s="16" t="inlineStr">
-        <is>
-          <t>C | 590呎 (3房)
-$1,324万
-$22,446/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
-        <is>
-          <t>A | 1339呎 (4+房)
-$5,223万
-$39,007/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>B | 1171呎 (4+房)
-$4,412万
-$37,677/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D33" s="17" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>天泷 - 2座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>56 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>7 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>44 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>5 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>A | 1181呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>B | 1006呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 1173呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="19" t="inlineStr">
-        <is>
-          <t>B | 1002呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 1173呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t>B | 920呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>A | 1173呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 920呎 (3房)
-$3,982万
-$43,283/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>A | 1173呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 920呎 (3房)
-$3,889万
-$42,272/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 1173呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 920呎 (3房)
-$3,638万
-$39,543/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>A | 1173呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 920呎 (3房)
-$3,610万
-$39,239/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>A | 1173呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 920呎 (3房)
-$3,454万
-$37,543/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 1076呎 (4+房)
-$4,590万
-$42,658/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 1002呎 (3房)
-$3,390万
-$33,832/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>A | 1173呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 1002呎 (3房)
-$3,345万
-$33,383/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 1173呎 (4+房)
-$4,111万
-$35,047/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 1002呎 (3房)
-$3,310万
-$33,034/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 1076呎 (4+房)
-$4,388万
-$40,781/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 920呎 (3房)
-$3,306万
-$35,935/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 1076呎 (4+房)
-$4,365万
-$40,567/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 1002呎 (3房)
-$3,286万
-$32,794/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 1173呎 (4+房)
-$4,100万
-$34,953/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 1002呎 (3房)
-$3,270万
-$32,635/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 1076呎 (4+房)
-$4,038万
-$37,528/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 920呎 (3房)
-$3,303万
-$35,902/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 1173呎 (4+房)
-$3,990万
-$34,015/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 1002呎 (3房)
-$3,228万
-$32,216/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 1173呎 (4+房)
-$3,965万
-$33,802/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 1002呎 (3房)
-$3,190万
-$31,836/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 1173呎 (4+房)
-$3,921万
-$33,427/呎
-(23年-11月)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 1002呎 (3房)
-$3,157万
-$31,507/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 1173呎 (4+房)
-$3,997万
-$34,075/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 920呎 (3房)
-$3,140万
-$34,130/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 1173呎 (4+房)
-$3,972万
-$33,862/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>B | 920呎 (3房)
-$3,219万
-$34,989/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A | 1173呎 (4+房)
-$3,861万
-$32,917/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>B | 1002呎 (3房)
-$3,130万
-$31,238/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>A | 1173呎 (4+房)
-$3,910万
-$33,333/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>B | 1002呎 (3房)
-$3,093万
-$30,868/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>A | 1076呎 (4+房)
-$3,836万
-$35,651/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>B | 1002呎 (3房)
-$3,103万
-$30,968/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 1173呎 (4+房)
-$3,854万
-$32,856/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>B | 920呎 (3房)
-$3,138万
-$34,109/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>A | 1173呎 (4+房)
-$3,780万
-$32,225/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>B | 920呎 (3房)
-$3,044万
-$33,087/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>A | 1076呎 (4+房)
-$3,730万
-$34,667/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>B | 920呎 (3房)
-$3,032万
-$32,957/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>A | 1076呎 (4+房)
-$3,715万
-$34,526/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>B | 920呎 (3房)
-$3,028万
-$32,913/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
-        <is>
-          <t>A | 1076呎 (4+房)
-$3,651万
-$33,931/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>B | 1002呎 (3房)
-$2,960万
-$29,541/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>天泷 - 3座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>111 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>4 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>45 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>62 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 1677呎 (4+房)
-$9,203万
-$54,880/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 1102呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 1085呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 1102呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 1085呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 1102呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 1085呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>A | 1102呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>B | 1085呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 1102呎 (3房)
-$4,042万
-$36,679/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 1085呎 (3房)
-$4,002万
-$36,885/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>A | 1102呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 994呎 (3房)
-$4,060万
-$40,845/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>A | 1102呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 994呎 (3房)
-$3,860万
-$38,833/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 1102呎 (3房)
-$3,774万
-$34,247/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 1085呎 (3房)
-$3,774万
-$34,783/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 1102呎 (3房)
-$3,708万
-$33,648/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 994呎 (3房)
-$3,752万
-$37,746/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 1027呎 (3房)
-$3,680万
-$35,833/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 994呎 (3房)
-$3,660万
-$36,821/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 1102呎 (3房)
-$3,671万
-$33,312/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 1085呎 (3房)
-$3,672万
-$33,843/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 1027呎 (3房)
-$4,114万
-$40,057/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 994呎 (3房)
-$4,960万
-$49,899/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 1102呎 (3房)
-$3,700万
-$33,575/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 994呎 (3房)
-$3,629万
-$36,509/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 1102呎 (3房)
-$3,627万
-$32,913/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 1085呎 (3房)
-$3,627万
-$33,428/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 1027呎 (3房)
-$3,584万
-$34,898/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 1085呎 (3房)
-$3,584万
-$33,032/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 1027呎 (3房)
-$3,563万
-$34,693/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 1085呎 (3房)
-$3,562万
-$32,832/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 1027呎 (3房)
-$3,593万
-$34,985/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 994呎 (3房)
-$3,540万
-$35,611/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 1102呎 (3房)
-$3,520万
-$31,942/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 1085呎 (3房)
-$3,518万
-$32,426/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 1102呎 (3房)
-$3,497万
-$31,730/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>B | 1085呎 (3房)
-$3,497万
-$32,228/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A | 1027呎 (3房)
-$3,880万
-$37,780/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>B | 994呎 (3房)
-$3,555万
-$35,765/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>A | 1102呎 (3房)
-$3,454万
-$31,338/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>B | 994呎 (3房)
-$3,454万
-$34,744/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>A | 1102呎 (3房)
-$3,464万
-$31,434/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>B | 1085呎 (3房)
-$3,524万
-$32,479/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 1102呎 (3房)
-$3,428万
-$31,107/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>B | 1085呎 (3房)
-$3,450万
-$31,797/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>A | 1102呎 (3房)
-$3,388万
-$30,744/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>B | 1085呎 (3房)
-$3,388万
-$31,226/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D30" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>A | 1102呎 (3房)
-$3,357万
-$30,463/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>B | 994呎 (3房)
-$3,351万
-$33,712/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D31" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E31" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>A | 1027呎 (3房)
-$3,323万
-$32,356/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>B | 1085呎 (3房)
-$3,290万
-$30,323/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D32" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E32" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
-        <is>
-          <t>A | 1102呎 (3房)
-$3,258万
-$29,564/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>B | 994呎 (3房)
-$3,530万
-$35,513/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D33" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E33" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>天泷 - 5座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>56 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>45 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>8 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>A | 1383呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>B | 1384呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 1382呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 1382呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 1382呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 1382呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 1382呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 1382呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>A | 1382呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 1382呎 (4+房)
-$6,036万
-$43,676/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>A | 1382呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 1282呎 (4+房)
-$5,982万
-$46,661/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 1282呎 (4+房)
-$5,591万
-$43,612/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 1382呎 (4+房)
-$5,390万
-$39,001/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 1382呎 (4+房)
-$5,373万
-$38,878/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 1382呎 (4+房)
-$5,373万
-$38,878/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>A | 1382呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 1282呎 (4+房)
-$5,432万
-$42,371/呎
-(25年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 1382呎 (4+房)
-$5,380万
-$38,929/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 1382呎 (4+房)
-$5,380万
-$38,929/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 1382呎 (4+房)
-$5,227万
-$37,822/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 1282呎 (4+房)
-$5,226万
-$40,767/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 1282呎 (4+房)
-$5,195万
-$40,523/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 1282呎 (4+房)
-$5,195万
-$40,523/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 1382呎 (4+房)
-$5,165万
-$37,370/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 1382呎 (4+房)
-$5,145万
-$37,229/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 1282呎 (4+房)
-$5,246万
-$40,919/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 1382呎 (4+房)
-$5,134万
-$37,151/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 1282呎 (4+房)
-$5,428万
-$42,340/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 1382呎 (4+房)
-$5,134万
-$37,149/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 1382呎 (4+房)
-$5,080万
-$36,758/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 1382呎 (4+房)
-$5,080万
-$36,758/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 1382呎 (4+房)
-$5,043万
-$36,491/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 1382呎 (4+房)
-$5,042万
-$36,484/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 1282呎 (4+房)
-$5,070万
-$39,548/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 1282呎 (4+房)
-$5,070万
-$39,548/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 1282呎 (4+房)
-$4,981万
-$38,853/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 1282呎 (4+房)
-$5,060万
-$39,470/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 1282呎 (4+房)
-$5,050万
-$39,392/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>B | 1282呎 (4+房)
-$5,050万
-$39,392/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A | 1282呎 (4+房)
-$4,898万
-$38,206/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>B | 1282呎 (4+房)
-$4,898万
-$38,206/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>A | 1282呎 (4+房)
-$4,995万
-$38,963/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>B | 1382呎 (4+房)
-$4,888万
-$35,371/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>A | 1282呎 (4+房)
-$4,966万
-$38,736/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>B | 1282呎 (4+房)
-$4,966万
-$38,736/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 1282呎 (4+房)
-$4,908万
-$38,284/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>B | 1282呎 (4+房)
-$4,908万
-$38,284/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>A | 1282呎 (4+房)
-$4,814万
-$37,549/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>B | 1282呎 (4+房)
-$4,819万
-$37,590/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>A | 1282呎 (4+房)
-$4,845万
-$37,793/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>B | 1282呎 (4+房)
-$4,961万
-$38,697/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>A | 1282呎 (4+房)
-$4,882万
-$38,081/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>B | 1282呎 (4+房)
-$4,753万
-$37,075/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
-        <is>
-          <t>A | 1282呎 (4+房)
-$4,868万
-$37,972/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>B | 1282呎 (4+房)
-$4,877万
-$38,042/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>天泷 - 6座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>111 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>7 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>38 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>64 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 1677呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 1085呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 1102呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 1085呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 1102呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 1085呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 1102呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>A | 1085呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>B | 1102呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>A | 1085呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>B | 1102呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 992呎 (3房)
-$4,469万
-$45,050/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 1027呎 (3房)
-$4,518万
-$43,992/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 992呎 (3房)
-$4,405万
-$44,405/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>B | 1102呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 992呎 (3房)
-$4,341万
-$43,760/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 1027呎 (3房)
-$4,427万
-$43,106/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 992呎 (3房)
-$4,217万
-$42,510/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 1102呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 992呎 (3房)
-$3,865万
-$38,962/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 1027呎 (3房)
-$4,300万
-$41,870/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 992呎 (3房)
-$3,843万
-$38,740/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 1027呎 (3房)
-$3,885万
-$37,829/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 992呎 (3房)
-$3,898万
-$39,294/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 1027呎 (3房)
-$4,129万
-$40,204/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 992呎 (3房)
-$3,820万
-$38,508/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 1027呎 (3房)
-$3,935万
-$38,315/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 992呎 (3房)
-$3,818万
-$38,488/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 1027呎 (3房)
-$3,878万
-$37,760/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>A | 1085呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 1102呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 992呎 (3房)
-$3,740万
-$37,702/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 1027呎 (3房)
-$3,780万
-$36,806/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 992呎 (3房)
-$3,730万
-$37,601/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 1027呎 (3房)
-$3,700万
-$36,027/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 992呎 (3房)
-$3,679万
-$37,087/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 1027呎 (3房)
-$3,728万
-$36,300/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 992呎 (3房)
-$3,600万
-$36,290/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>B | 1027呎 (3房)
-$3,640万
-$35,443/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A | 1085呎 (3房)
-$3,587万
-$33,060/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>B | 1102呎 (3房)
-$3,618万
-$32,831/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>A | 992呎 (3房)
-$3,565万
-$35,938/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>B | 1102呎 (3房)
-$3,603万
-$32,695/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>A | 992呎 (3房)
-$3,626万
-$36,552/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>B | 1027呎 (3房)
-$3,664万
-$35,677/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 992呎 (3房)
-$3,453万
-$34,808/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>B | 1027呎 (3房)
-$3,653万
-$35,570/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>A | 992呎 (3房)
-$3,274万
-$33,004/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>B | 1042呎 (3房)
-$3,771万
-$36,190/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D30" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>A | 1085呎 (3房)
-$3,230万
-$29,770/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C31" s="16" t="inlineStr">
-        <is>
-          <t>B | 1042呎 (3房)
-$3,193万
-$30,643/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D31" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E31" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>A | 992呎 (3房)
-$3,184万
-$32,097/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C32" s="19" t="inlineStr">
-        <is>
-          <t>B | 1117呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D32" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E32" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
-        <is>
-          <t>A | 1085呎 (3房)
-$3,127万
-$28,820/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C33" s="19" t="inlineStr">
-        <is>
-          <t>B | 1117呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D33" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E33" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>天泷 - 7座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>48 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>39 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>6 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>A | 1006呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>B | 1182呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 1002呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 1173呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 1002呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 1173呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>A | 1002呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>B | 1173呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 920呎 (3房)
-$4,111万
-$44,685/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>B | 1173呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 920呎 (3房)
-$3,835万
-$41,685/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 1076呎 (4+房)
-$4,636万
-$43,086/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 920呎 (3房)
-$3,675万
-$39,946/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 1076呎 (4+房)
-$4,430万
-$41,171/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 920呎 (3房)
-$3,643万
-$39,598/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 1076呎 (4+房)
-$4,405万
-$40,939/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 1002呎 (3房)
-$3,613万
-$36,058/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 1173呎 (4+房)
-$4,370万
-$37,255/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 920呎 (3房)
-$3,580万
-$38,913/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 1076呎 (4+房)
-$4,345万
-$40,381/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 920呎 (3房)
-$3,534万
-$38,413/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 1076呎 (4+房)
-$4,298万
-$39,944/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 920呎 (3房)
-$3,472万
-$37,739/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 1173呎 (4+房)
-$4,214万
-$35,925/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 920呎 (3房)
-$3,513万
-$38,185/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 1076呎 (4+房)
-$4,246万
-$39,461/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 920呎 (3房)
-$3,498万
-$38,022/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 1076呎 (4+房)
-$4,228万
-$39,294/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 920呎 (3房)
-$3,421万
-$37,185/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 1173呎 (4+房)
-$4,140万
-$35,294/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 1002呎 (3房)
-$3,395万
-$33,882/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 1076呎 (4+房)
-$4,188万
-$38,922/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 920呎 (3房)
-$3,380万
-$36,739/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 1076呎 (4+房)
-$4,090万
-$38,011/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 920呎 (3房)
-$3,359万
-$36,511/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 1173呎 (4+房)
-$4,066万
-$34,663/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 920呎 (3房)
-$3,330万
-$36,196/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 1076呎 (4+房)
-$4,037万
-$37,519/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 920呎 (3房)
-$3,318万
-$36,065/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>B | 1173呎 (4+房)
-$4,016万
-$34,237/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A | 1002呎 (3房)
-$3,290万
-$32,834/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>B | 1076呎 (3房)
-$4,087万
-$37,983/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>A | 920呎 (3房)
-$3,271万
-$35,554/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>B | 1076呎 (4+房)
-$3,958万
-$36,784/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>A | 920呎 (3房)
-$3,295万
-$35,815/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>B | 1076呎 (4+房)
-$3,988万
-$37,063/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>A | 920呎 (3房)
-$3,416万
-$37,130/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>B | 1173呎 (4+房)
-$4,058万
-$34,595/呎
-(26年-06月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>天泷 - 8座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>95 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>7 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>24 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>64 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 1890呎 (4+房)
-$10,395万
-$55,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 1259呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 1298呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 1259呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 1298呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 1259呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 1298呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 1259呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 1298呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 1259呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 1298呎 (4+房)
-$5,013万
-$38,621/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 1165呎 (4+房)
-$5,381万
-$46,189/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 1298呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>A | 1259呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 1298呎 (4+房)
-$4,936万
-$38,028/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 1165呎 (4+房)
-$4,898万
-$42,043/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>B | 1298呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>A | 1259呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>B | 1298呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 1259呎 (4+房)
-$4,712万
-$37,426/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 1298呎 (4+房)
-$4,808万
-$37,042/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 1259呎 (4+房)
-$4,663万
-$37,037/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 1298呎 (4+房)
-$4,771万
-$36,757/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 1165呎 (4+房)
-$4,988万
-$42,815/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 1204呎 (4+房)
-$5,103万
-$42,384/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 1259呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 1298呎 (4+房)
-$4,765万
-$36,710/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>A | 1259呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 1298呎 (4+房)
-$4,688万
-$36,117/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 1165呎 (4+房)
-$4,800万
-$41,202/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 1298呎 (4+房)
-$4,657万
-$35,878/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 1259呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 1298呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 1165呎 (4+房)
-$4,750万
-$40,773/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 1204呎 (4+房)
-$5,153万
-$42,799/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 1165呎 (4+房)
-$4,548万
-$39,039/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 1298呎 (4+房)
-$4,646万
-$35,794/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 1165呎 (4+房)
-$4,930万
-$42,318/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>B | 1204呎 (4+房)
-$4,977万
-$41,337/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A | 1165呎 (4+房)
-$4,550万
-$39,056/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>B | 1298呎 (4+房)
-$4,900万
-$37,750/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>A | 1165呎 (4+房)
-$4,520万
-$38,798/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C27" s="19" t="inlineStr">
-        <is>
-          <t>B | 1298呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B28" s="19" t="inlineStr">
-        <is>
-          <t>A | 1259呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>B | 1298呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>A | 1259呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>B | 1298呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>C | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>D | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>天泷 - Harbour Mansion 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>7 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>7 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 908呎 (3房)
-$3,904万
-$43,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 900呎 (3房)
-$3,199万
-$35,544/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 836呎 (3房)
-$2,949万
-$35,280/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 907呎 (3房)
-$3,127万
-$34,472/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 900呎 (3房)
-$3,397万
-$37,750/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 836呎 (3房)
-$2,680万
-$32,060/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 907呎 (3房)
-$2,916万
-$32,151/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-启德-天泷.xlsx
+++ b/files/九龙-启德-天泷.xlsx
@@ -8,6 +8,14 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6座" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7座" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8座" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Harbour Mansion" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +27,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +49,102 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +155,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +236,63 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +669,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -27617,4 +27812,6812 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1942呎 (4+房)
+$11215万
+$57,750/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>C | 635呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 1428呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 1258呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 590呎 (3房)
+$1617万
+$27,399/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 1428呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 1258呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 590呎 (3房)
+$1568万
+$26,576/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 1428呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 1258呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 590呎 (3房)
+$1588万
+$26,907/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>A | 1428呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>B | 1258呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 590呎 (3房)
+$1540万
+$26,099/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 1339呎 (4+房)
+$6740万
+$50,336/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 1258呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 590呎 (3房)
+$1575万
+$26,692/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 1339呎 (4+房)
+$6665万
+$49,776/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>B | 1258呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 590呎 (3房)
+$1568万
+$26,584/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 1339呎 (4+房)
+$6007万
+$44,862/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>B | 1258呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 590呎 (3房)
+$1562万
+$26,476/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 1339呎 (4+房)
+$6453万
+$48,193/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 1171呎 (4+房)
+$5285万
+$45,132/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 590呎 (3房)
+$1509万
+$25,577/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 1428呎 (4+房)
+$5860万
+$41,036/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 1171呎 (4+房)
+$4868万
+$41,571/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 590呎 (3房)
+$1497万
+$25,369/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 1339呎 (4+房)
+$5810万
+$43,391/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>B | 1258呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 590呎 (3房)
+$1537万
+$26,046/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 1339呎 (4+房)
+$6161万
+$46,012/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 1171呎 (4+房)
+$4900万
+$41,845/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 590呎 (3房)
+$1491万
+$25,264/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 1428呎 (4+房)
+$5733万
+$40,146/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 1171呎 (4+房)
+$4756万
+$40,615/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 590呎 (3房)
+$1524万
+$25,831/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 1339呎 (3房)
+$5832万
+$43,555/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 1171呎 (4+房)
+$4719万
+$40,299/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 590呎 (3房)
+$1465万
+$24,825/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 1339呎 (4+房)
+$5976万
+$44,630/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>B | 1258呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 590呎 (3房)
+$1511万
+$25,615/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 1428呎 (4+房)
+$5633万
+$39,447/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 1171呎 (4+房)
+$4568万
+$39,009/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 590呎 (3房)
+$1486万
+$25,185/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 1339呎 (4+房)
+$5550万
+$41,449/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 1171呎 (4+房)
+$4502万
+$38,446/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 590呎 (3房)
+$1461万
+$24,763/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 1428呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 1258呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 590呎 (3房)
+$1405万
+$23,814/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 1339呎 (4+房)
+$5657万
+$42,248/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>B | 1258呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 590呎 (3房)
+$1440万
+$24,410/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 1428呎 (4+房)
+$5614万
+$39,314/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 1171呎 (4+房)
+$4763万
+$40,675/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 590呎 (3房)
+$1422万
+$24,108/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 1339呎 (4+房)
+$5468万
+$40,833/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 1171呎 (4+房)
+$4711万
+$40,231/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 590呎 (3房)
+$1416万
+$24,001/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 1339呎 (4+房)
+$5558万
+$41,509/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 1171呎 (4+房)
+$4510万
+$38,514/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 590呎 (3房)
+$1410万
+$23,893/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 1339呎 (4+房)
+$5546万
+$41,419/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 1171呎 (4+房)
+$4493万
+$38,369/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 590呎 (3房)
+$1407万
+$23,839/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 1339呎 (4+房)
+$5365万
+$40,067/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 1171呎 (4+房)
+$4557万
+$38,915/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>C | 590呎 (3房)
+$1361万
+$23,072/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 1339呎 (4+房)
+$5432万
+$40,568/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 1171呎 (4+房)
+$4408万
+$37,643/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>C | 590呎 (3房)
+$1397万
+$23,678/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>A | 1339呎 (4+房)
+$5393万
+$40,275/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 1171呎 (4+房)
+$4379万
+$37,395/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>C | 590呎 (3房)
+$1349万
+$22,864/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>A | 1339呎 (4+房)
+$5327万
+$39,783/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>B | 1171呎 (4+房)
+$4460万
+$38,087/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>C | 590呎 (3房)
+$1324万
+$22,446/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>A | 1339呎 (4+房)
+$5223万
+$39,007/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>B | 1171呎 (4+房)
+$4412万
+$37,677/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D32" s="21" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>A | 1181呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>B | 1006呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 1173呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>B | 1002呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 1173呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>B | 920呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>A | 1173呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 920呎 (3房)
+$3982万
+$43,283/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>A | 1173呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 920呎 (3房)
+$3889万
+$42,272/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 1173呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 920呎 (3房)
+$3638万
+$39,543/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>A | 1173呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 920呎 (3房)
+$3610万
+$39,239/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>A | 1173呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 920呎 (3房)
+$3454万
+$37,543/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 1076呎 (4+房)
+$4590万
+$42,658/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 1002呎 (3房)
+$3390万
+$33,832/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>A | 1173呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 1002呎 (3房)
+$3345万
+$33,383/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 1173呎 (4+房)
+$4111万
+$35,047/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 1002呎 (3房)
+$3310万
+$33,034/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 1076呎 (4+房)
+$4388万
+$40,781/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 920呎 (3房)
+$3306万
+$35,935/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 1076呎 (4+房)
+$4365万
+$40,567/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 1002呎 (3房)
+$3286万
+$32,794/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 1173呎 (4+房)
+$4100万
+$34,953/呎
+(23年-05月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 1002呎 (3房)
+$3270万
+$32,635/呎
+(24年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 1076呎 (4+房)
+$4038万
+$37,528/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 920呎 (3房)
+$3303万
+$35,902/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 1173呎 (4+房)
+$3990万
+$34,015/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 1002呎 (3房)
+$3228万
+$32,216/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 1173呎 (4+房)
+$3965万
+$33,802/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 1002呎 (3房)
+$3190万
+$31,836/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 1173呎 (4+房)
+$3921万
+$33,427/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 1002呎 (3房)
+$3157万
+$31,507/呎
+(23年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 1173呎 (4+房)
+$3997万
+$34,075/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 920呎 (3房)
+$3140万
+$34,130/呎
+(24年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 1173呎 (4+房)
+$3972万
+$33,862/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 920呎 (3房)
+$3219万
+$34,989/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 1173呎 (4+房)
+$3861万
+$32,917/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 1002呎 (3房)
+$3130万
+$31,238/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 1173呎 (4+房)
+$3910万
+$33,333/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 1002呎 (3房)
+$3093万
+$30,868/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 1076呎 (4+房)
+$3836万
+$35,651/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 1002呎 (3房)
+$3103万
+$30,968/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 1173呎 (4+房)
+$3854万
+$32,856/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 920呎 (3房)
+$3138万
+$34,109/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 1173呎 (4+房)
+$3780万
+$32,225/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 920呎 (3房)
+$3044万
+$33,087/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>A | 1076呎 (4+房)
+$3730万
+$34,667/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 920呎 (3房)
+$3032万
+$32,957/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>A | 1076呎 (4+房)
+$3715万
+$34,526/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>B | 920呎 (3房)
+$3028万
+$32,913/呎
+(25年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>A | 1076呎 (4+房)
+$3651万
+$33,931/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>B | 1002呎 (3房)
+$2960万
+$29,541/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>3座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1677呎 (4+房)
+$9203万
+$54,880/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 1102呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 1085呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 1102呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 1085呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 1102呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 1085呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>A | 1102呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>B | 1085呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 1102呎 (3房)
+$4042万
+$36,679/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 1085呎 (3房)
+$4002万
+$36,885/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>A | 1102呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 994呎 (3房)
+$4060万
+$40,845/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>A | 1102呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 994呎 (3房)
+$3860万
+$38,833/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 1102呎 (3房)
+$3774万
+$34,247/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 1085呎 (3房)
+$3774万
+$34,783/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 1102呎 (3房)
+$3708万
+$33,648/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 994呎 (3房)
+$3752万
+$37,746/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 1027呎 (3房)
+$3680万
+$35,833/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 994呎 (3房)
+$3660万
+$36,821/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 1102呎 (3房)
+$3671万
+$33,312/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 1085呎 (3房)
+$3672万
+$33,843/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 1027呎 (3房)
+$4114万
+$40,057/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 994呎 (3房)
+$4960万
+$49,899/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 1102呎 (3房)
+$3700万
+$33,575/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 994呎 (3房)
+$3629万
+$36,509/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 1102呎 (3房)
+$3627万
+$32,913/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 1085呎 (3房)
+$3627万
+$33,428/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 1027呎 (3房)
+$3584万
+$34,898/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 1085呎 (3房)
+$3584万
+$33,032/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 1027呎 (3房)
+$3563万
+$34,693/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 1085呎 (3房)
+$3562万
+$32,832/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 1027呎 (3房)
+$3593万
+$34,985/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 994呎 (3房)
+$3540万
+$35,611/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 1102呎 (3房)
+$3520万
+$31,942/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 1085呎 (3房)
+$3518万
+$32,426/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 1102呎 (3房)
+$3497万
+$31,730/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 1085呎 (3房)
+$3497万
+$32,228/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 1027呎 (3房)
+$3880万
+$37,780/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 994呎 (3房)
+$3555万
+$35,765/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 1102呎 (3房)
+$3454万
+$31,338/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 994呎 (3房)
+$3454万
+$34,744/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 1102呎 (3房)
+$3464万
+$31,434/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 1085呎 (3房)
+$3524万
+$32,479/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 1102呎 (3房)
+$3428万
+$31,107/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 1085呎 (3房)
+$3450万
+$31,797/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 1102呎 (3房)
+$3388万
+$30,744/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 1085呎 (3房)
+$3388万
+$31,226/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>A | 1102呎 (3房)
+$3357万
+$30,463/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 994呎 (3房)
+$3351万
+$33,712/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>A | 1027呎 (3房)
+$3323万
+$32,356/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>B | 1085呎 (3房)
+$3290万
+$30,323/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>A | 1102呎 (3房)
+$3258万
+$29,564/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>B | 994呎 (3房)
+$3530万
+$35,513/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>5座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>A | 1383呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>B | 1384呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 1382呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 1382呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 1382呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 1382呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 1382呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 1382呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>A | 1382呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 1382呎 (4+房)
+$6036万
+$43,676/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>A | 1382呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 1282呎 (4+房)
+$5982万
+$46,661/呎
+(26年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 1282呎 (4+房)
+$5591万
+$43,612/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 1382呎 (4+房)
+$5390万
+$39,001/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 1382呎 (4+房)
+$5373万
+$38,878/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 1382呎 (4+房)
+$5373万
+$38,878/呎
+(25年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>A | 1382呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 1282呎 (4+房)
+$5432万
+$42,371/呎
+(25年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 1382呎 (4+房)
+$5380万
+$38,929/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 1382呎 (4+房)
+$5380万
+$38,929/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 1382呎 (4+房)
+$5227万
+$37,822/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 1282呎 (4+房)
+$5226万
+$40,767/呎
+(24年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 1282呎 (4+房)
+$5195万
+$40,523/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 1282呎 (4+房)
+$5195万
+$40,523/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 1382呎 (4+房)
+$5165万
+$37,370/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 1382呎 (4+房)
+$5145万
+$37,229/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 1282呎 (4+房)
+$5246万
+$40,919/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 1382呎 (4+房)
+$5134万
+$37,151/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 1282呎 (4+房)
+$5428万
+$42,340/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 1382呎 (4+房)
+$5134万
+$37,149/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 1382呎 (4+房)
+$5080万
+$36,758/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 1382呎 (4+房)
+$5080万
+$36,758/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 1382呎 (4+房)
+$5043万
+$36,491/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 1382呎 (4+房)
+$5042万
+$36,484/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 1282呎 (4+房)
+$5070万
+$39,548/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 1282呎 (4+房)
+$5070万
+$39,548/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 1282呎 (4+房)
+$4981万
+$38,853/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 1282呎 (4+房)
+$5060万
+$39,470/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 1282呎 (4+房)
+$5050万
+$39,392/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 1282呎 (4+房)
+$5050万
+$39,392/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 1282呎 (4+房)
+$4898万
+$38,206/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 1282呎 (4+房)
+$4898万
+$38,206/呎
+(25年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 1282呎 (4+房)
+$4995万
+$38,963/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 1382呎 (4+房)
+$4888万
+$35,371/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 1282呎 (4+房)
+$4966万
+$38,736/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 1282呎 (4+房)
+$4966万
+$38,736/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 1282呎 (4+房)
+$4908万
+$38,284/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 1282呎 (4+房)
+$4908万
+$38,284/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 1282呎 (4+房)
+$4814万
+$37,549/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 1282呎 (4+房)
+$4819万
+$37,590/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>A | 1282呎 (4+房)
+$4845万
+$37,793/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 1282呎 (4+房)
+$4961万
+$38,697/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>A | 1282呎 (4+房)
+$4882万
+$38,081/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>B | 1282呎 (4+房)
+$4753万
+$37,075/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>A | 1282呎 (4+房)
+$4868万
+$37,972/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>B | 1282呎 (4+房)
+$4877万
+$38,042/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>6座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>A | 1677呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 1085呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 1102呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 1085呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 1102呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 1085呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 1102呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>A | 1085呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>B | 1102呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>A | 1085呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>B | 1102呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 992呎 (3房)
+$4469万
+$45,050/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 1027呎 (3房)
+$4518万
+$43,992/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 992呎 (3房)
+$4405万
+$44,405/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>B | 1102呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 992呎 (3房)
+$4341万
+$43,760/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 1027呎 (3房)
+$4427万
+$43,106/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 992呎 (3房)
+$4217万
+$42,510/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 1102呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 992呎 (3房)
+$3865万
+$38,962/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 1027呎 (3房)
+$4300万
+$41,870/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 992呎 (3房)
+$3843万
+$38,740/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 1027呎 (3房)
+$3885万
+$37,829/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 992呎 (3房)
+$3898万
+$39,294/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 1027呎 (3房)
+$4129万
+$40,204/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 992呎 (3房)
+$3820万
+$38,508/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 1027呎 (3房)
+$3935万
+$38,315/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 992呎 (3房)
+$3818万
+$38,488/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 1027呎 (3房)
+$3878万
+$37,760/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>A | 1085呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 1102呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 992呎 (3房)
+$3740万
+$37,702/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 1027呎 (3房)
+$3780万
+$36,806/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 992呎 (3房)
+$3730万
+$37,601/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 1027呎 (3房)
+$3700万
+$36,027/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 992呎 (3房)
+$3679万
+$37,087/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 1027呎 (3房)
+$3728万
+$36,300/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 992呎 (3房)
+$3600万
+$36,290/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 1027呎 (3房)
+$3640万
+$35,443/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 1085呎 (3房)
+$3587万
+$33,060/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 1102呎 (3房)
+$3618万
+$32,831/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 992呎 (3房)
+$3565万
+$35,938/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 1102呎 (3房)
+$3603万
+$32,695/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 992呎 (3房)
+$3626万
+$36,552/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 1027呎 (3房)
+$3664万
+$35,677/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 992呎 (3房)
+$3453万
+$34,808/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 1027呎 (3房)
+$3653万
+$35,570/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>A | 992呎 (3房)
+$3274万
+$33,004/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>B | 1042呎 (3房)
+$3771万
+$36,190/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
+        <is>
+          <t>A | 1085呎 (3房)
+$3230万
+$29,770/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>B | 1042呎 (3房)
+$3193万
+$30,643/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>A | 992呎 (3房)
+$3184万
+$32,097/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>B | 1117呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
+        <is>
+          <t>A | 1085呎 (3房)
+$3127万
+$28,820/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C32" s="23" t="inlineStr">
+        <is>
+          <t>B | 1117呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>7座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>A | 1006呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>B | 1182呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 1002呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 1173呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 1002呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 1173呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>A | 1002呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>B | 1173呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 920呎 (3房)
+$4111万
+$44,685/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>B | 1173呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 920呎 (3房)
+$3835万
+$41,685/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 1076呎 (4+房)
+$4636万
+$43,086/呎
+(26年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 920呎 (3房)
+$3675万
+$39,946/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 1076呎 (4+房)
+$4430万
+$41,171/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 920呎 (3房)
+$3643万
+$39,598/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 1076呎 (4+房)
+$4405万
+$40,939/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 1002呎 (3房)
+$3613万
+$36,058/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 1173呎 (4+房)
+$4370万
+$37,255/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 920呎 (3房)
+$3580万
+$38,913/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 1076呎 (4+房)
+$4345万
+$40,381/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 920呎 (3房)
+$3534万
+$38,413/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 1076呎 (4+房)
+$4298万
+$39,944/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 920呎 (3房)
+$3472万
+$37,739/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 1173呎 (4+房)
+$4214万
+$35,925/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 920呎 (3房)
+$3513万
+$38,185/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 1076呎 (4+房)
+$4246万
+$39,461/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 920呎 (3房)
+$3498万
+$38,022/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 1076呎 (4+房)
+$4228万
+$39,294/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 920呎 (3房)
+$3421万
+$37,185/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 1173呎 (4+房)
+$4140万
+$35,294/呎
+(25年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 1002呎 (3房)
+$3395万
+$33,882/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 1076呎 (4+房)
+$4188万
+$38,922/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 920呎 (3房)
+$3380万
+$36,739/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 1076呎 (4+房)
+$4090万
+$38,011/呎
+(25年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 920呎 (3房)
+$3359万
+$36,511/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 1173呎 (4+房)
+$4066万
+$34,663/呎
+(24年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 920呎 (3房)
+$3330万
+$36,196/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 1076呎 (4+房)
+$4037万
+$37,519/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 920呎 (3房)
+$3318万
+$36,065/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 1173呎 (4+房)
+$4016万
+$34,237/呎
+(25年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 1002呎 (3房)
+$3290万
+$32,834/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 1076呎 (3房)
+$4087万
+$37,983/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 920呎 (3房)
+$3271万
+$35,554/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 1076呎 (4+房)
+$3958万
+$36,784/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 920呎 (3房)
+$3295万
+$35,815/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 1076呎 (4+房)
+$3988万
+$37,063/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>A | 920呎 (3房)
+$3416万
+$37,130/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 1076呎 (4+房)
+$4058万
+$37,714/呎
+(26年-07月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>8座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1890呎 (4+房)
+$10395万
+$55,000/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 1259呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 1298呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 1259呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 1298呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 1259呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 1298呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 1259呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 1298呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 1259呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 1298呎 (4+房)
+$5013万
+$38,621/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 1165呎 (4+房)
+$5381万
+$46,189/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 1298呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>A | 1259呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 1298呎 (4+房)
+$4936万
+$38,028/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 1165呎 (4+房)
+$4898万
+$42,043/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>B | 1298呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>A | 1259呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>B | 1298呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 1259呎 (4+房)
+$4712万
+$37,426/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 1298呎 (4+房)
+$4808万
+$37,042/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 1259呎 (4+房)
+$4663万
+$37,037/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 1298呎 (4+房)
+$4771万
+$36,757/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 1165呎 (4+房)
+$4988万
+$42,815/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 1204呎 (4+房)
+$5103万
+$42,384/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 1259呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 1298呎 (4+房)
+$4765万
+$36,710/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>A | 1259呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 1298呎 (4+房)
+$4688万
+$36,117/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 1165呎 (4+房)
+$4800万
+$41,202/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 1298呎 (4+房)
+$4657万
+$35,878/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 1259呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 1298呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 1165呎 (4+房)
+$4750万
+$40,773/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 1204呎 (4+房)
+$5153万
+$42,799/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 1165呎 (4+房)
+$4548万
+$39,039/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 1298呎 (4+房)
+$4646万
+$35,794/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 1165呎 (4+房)
+$4930万
+$42,318/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 1204呎 (4+房)
+$4977万
+$41,337/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 1165呎 (4+房)
+$4550万
+$39,056/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 1298呎 (4+房)
+$4900万
+$37,750/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 1165呎 (4+房)
+$4520万
+$38,798/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>B | 1298呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>A | 1259呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 1298呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A | 1259呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 1298呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>D | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Harbour Mansion 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 908呎 (3房)
+$3904万
+$43,000/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 900呎 (3房)
+$3199万
+$35,544/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 836呎 (3房)
+$2949万
+$35,280/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 907呎 (3房)
+$3127万
+$34,472/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 900呎 (3房)
+$3397万
+$37,750/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 836呎 (3房)
+$2680万
+$32,060/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 907呎 (3房)
+$2916万
+$32,151/呎
+(23年-07月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-启德-天泷.xlsx
+++ b/files/九龙-启德-天泷.xlsx
@@ -669,7 +669,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -26817,7 +26817,7 @@
         </is>
       </c>
       <c r="E548" s="4" t="n">
-        <v>1298</v>
+        <v>1204</v>
       </c>
       <c r="F548" s="3" t="inlineStr">
         <is>
@@ -26826,14 +26826,14 @@
       </c>
       <c r="G548" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H548" s="5" t="n">
         <v>49000000</v>
       </c>
       <c r="I548" s="5" t="n">
-        <v>37750</v>
+        <v>40698</v>
       </c>
       <c r="J548" s="3" t="inlineStr">
         <is>
@@ -34277,10 +34277,10 @@
       </c>
       <c r="C25" s="20" t="inlineStr">
         <is>
-          <t>B | 1298呎 (4+房)
+          <t>B | 1204呎 (4+房)
 $4900万
-$37,750/呎
-(26年-06月)</t>
+$40,698/呎
+(26年-07月)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">

--- a/files/九龙-启德-天泷.xlsx
+++ b/files/九龙-启德-天泷.xlsx
@@ -3607,7 +3607,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
@@ -3647,7 +3647,7 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4407,7 +4407,7 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>1258</v>
+        <v>1171</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
@@ -11203,12 +11203,12 @@
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I158" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J158" s="3" t="inlineStr">
@@ -11218,12 +11218,12 @@
       </c>
       <c r="K158" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L158" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M158" s="3" t="inlineStr">
@@ -11233,7 +11233,7 @@
       </c>
       <c r="N158" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -11263,7 +11263,7 @@
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
@@ -11273,12 +11273,12 @@
       </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I159" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J159" s="3" t="inlineStr">
@@ -11288,12 +11288,12 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L159" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M159" s="3" t="inlineStr">
@@ -11303,7 +11303,7 @@
       </c>
       <c r="N159" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -18153,7 +18153,7 @@
         </is>
       </c>
       <c r="E260" s="4" t="n">
-        <v>1382</v>
+        <v>1282</v>
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
@@ -18162,14 +18162,14 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
         <v>60360000</v>
       </c>
       <c r="I260" s="5" t="n">
-        <v>43676</v>
+        <v>47083</v>
       </c>
       <c r="J260" s="3" t="inlineStr">
         <is>
@@ -23359,7 +23359,7 @@
       </c>
       <c r="F337" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G337" s="3" t="inlineStr">
@@ -23369,12 +23369,12 @@
       </c>
       <c r="H337" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I337" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J337" s="3" t="inlineStr">
@@ -23384,12 +23384,12 @@
       </c>
       <c r="K337" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L337" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M337" s="3" t="inlineStr">
@@ -23399,7 +23399,7 @@
       </c>
       <c r="N337" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -28543,7 +28543,7 @@
       </c>
       <c r="F413" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G413" s="3" t="inlineStr">
@@ -28553,12 +28553,12 @@
       </c>
       <c r="H413" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I413" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J413" s="3" t="inlineStr">
@@ -28568,12 +28568,12 @@
       </c>
       <c r="K413" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L413" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M413" s="3" t="inlineStr">
@@ -28583,7 +28583,7 @@
       </c>
       <c r="N413" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -39220,7 +39220,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -39240,7 +39240,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -39707,12 +39707,12 @@
 (26年-03月-29日)</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>B | 1258呎 (4+房)
-招标单位
--
-(在售)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -39833,7 +39833,7 @@
       </c>
       <c r="C23" s="23" t="inlineStr">
         <is>
-          <t>B | 1258呎 (4+房)
+          <t>B | 1171呎 (4+房)
 招标单位
 -
 (在售)</t>
@@ -40947,7 +40947,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -40967,7 +40967,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>64</t>
         </is>
       </c>
     </row>
@@ -41153,20 +41153,20 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 1102呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C9" s="23" t="inlineStr">
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 1085呎 (3房)
-招标单位
--
-(在售)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -42302,10 +42302,10 @@
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>B | 1382呎 (4+房)
+          <t>B | 1282呎 (4+房)
 $6036万
-$43,676/呎
-(26年-06月-14日)</t>
+$47,083/呎
+(26年-07月-16日)</t>
         </is>
       </c>
     </row>
@@ -42910,7 +42910,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -42930,7 +42930,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>66</t>
         </is>
       </c>
     </row>
@@ -43241,12 +43241,12 @@
 (26年-04月-16日)</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 1102呎 (3房)
-招标单位
--
-(在售)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -43982,12 +43982,12 @@
 (25年-04月-07日)</t>
         </is>
       </c>
-      <c r="C31" s="23" t="inlineStr">
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>B | 1117呎 (3房)
-招标单位
--
-(在售)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">

--- a/files/九龙-启德-天泷.xlsx
+++ b/files/九龙-启德-天泷.xlsx
@@ -4411,23 +4411,19 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>47900000</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>40905</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
@@ -4436,12 +4432,12 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
@@ -4451,7 +4447,7 @@
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -39220,7 +39216,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -39230,7 +39226,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>66</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -39277,7 +39273,7 @@
           <t>A | 1942呎 (4+房)
 $11215万
 $57,750/呎
-(23年-06月-13日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -39317,7 +39313,7 @@
           <t>C | 590呎 (3房)
 $1617万
 $27,399/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -39348,7 +39344,7 @@
           <t>C | 590呎 (3房)
 $1568万
 $26,576/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -39379,7 +39375,7 @@
           <t>C | 590呎 (3房)
 $1588万
 $26,907/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -39410,7 +39406,7 @@
           <t>C | 590呎 (3房)
 $1540万
 $26,099/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -39425,7 +39421,7 @@
           <t>A | 1339呎 (4+房)
 $6740万
 $50,336/呎
-(26年-06月-28日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -39441,7 +39437,7 @@
           <t>C | 590呎 (3房)
 $1575万
 $26,692/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -39456,7 +39452,7 @@
           <t>A | 1339呎 (4+房)
 $6665万
 $49,776/呎
-(26年-06月-16日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -39472,7 +39468,7 @@
           <t>C | 590呎 (3房)
 $1568万
 $26,584/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -39487,7 +39483,7 @@
           <t>A | 1339呎 (4+房)
 $6007万
 $44,862/呎
-(25年-06月-03日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
@@ -39503,7 +39499,7 @@
           <t>C | 590呎 (3房)
 $1562万
 $26,476/呎
-(26年-03月-18日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -39518,7 +39514,7 @@
           <t>A | 1339呎 (4+房)
 $6453万
 $48,193/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -39526,7 +39522,7 @@
           <t>B | 1171呎 (4+房)
 $5285万
 $45,132/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -39534,7 +39530,7 @@
           <t>C | 590呎 (3房)
 $1509万
 $25,577/呎
-(26年-04月-13日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -39549,7 +39545,7 @@
           <t>A | 1428呎 (4+房)
 $5860万
 $41,036/呎
-(24年-05月-26日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -39557,7 +39553,7 @@
           <t>B | 1171呎 (4+房)
 $4868万
 $41,571/呎
-(25年-10月-20日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -39565,7 +39561,7 @@
           <t>C | 590呎 (3房)
 $1497万
 $25,369/呎
-(26年-03月-02日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -39580,7 +39576,7 @@
           <t>A | 1339呎 (4+房)
 $5810万
 $43,391/呎
-(25年-06月-03日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="C15" s="24" t="inlineStr">
@@ -39596,7 +39592,7 @@
           <t>C | 590呎 (3房)
 $1537万
 $26,046/呎
-(26年-03月-10日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -39611,7 +39607,7 @@
           <t>A | 1339呎 (4+房)
 $6161万
 $46,012/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -39619,7 +39615,7 @@
           <t>B | 1171呎 (4+房)
 $4900万
 $41,845/呎
-(26年-02月-05日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -39627,7 +39623,7 @@
           <t>C | 590呎 (3房)
 $1491万
 $25,264/呎
-(26年-03月-12日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -39642,7 +39638,7 @@
           <t>A | 1428呎 (4+房)
 $5733万
 $40,146/呎
-(25年-01月-05日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -39650,7 +39646,7 @@
           <t>B | 1171呎 (4+房)
 $4756万
 $40,615/呎
-(25年-11月-26日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -39658,7 +39654,7 @@
           <t>C | 590呎 (3房)
 $1524万
 $25,831/呎
-(26年-03月-02日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -39673,7 +39669,7 @@
           <t>A | 1339呎 (3房)
 $5832万
 $43,555/呎
-(25年-12月-30日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -39681,7 +39677,7 @@
           <t>B | 1171呎 (4+房)
 $4719万
 $40,299/呎
-(25年-12月-30日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -39689,7 +39685,7 @@
           <t>C | 590呎 (3房)
 $1465万
 $24,825/呎
-(26年-02月-25日)</t>
+(26年-02月)</t>
         </is>
       </c>
     </row>
@@ -39704,7 +39700,7 @@
           <t>A | 1339呎 (4+房)
 $5976万
 $44,630/呎
-(26年-03月-29日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -39720,7 +39716,7 @@
           <t>C | 590呎 (3房)
 $1511万
 $25,615/呎
-(26年-03月-16日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -39735,7 +39731,7 @@
           <t>A | 1428呎 (4+房)
 $5633万
 $39,447/呎
-(25年-06月-03日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -39743,7 +39739,7 @@
           <t>B | 1171呎 (4+房)
 $4568万
 $39,009/呎
-(25年-06月-08日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -39751,7 +39747,7 @@
           <t>C | 590呎 (3房)
 $1486万
 $25,185/呎
-(26年-03月-01日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -39766,7 +39762,7 @@
           <t>A | 1339呎 (4+房)
 $5550万
 $41,449/呎
-(25年-05月-13日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -39774,7 +39770,7 @@
           <t>B | 1171呎 (4+房)
 $4502万
 $38,446/呎
-(25年-05月-13日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -39782,7 +39778,7 @@
           <t>C | 590呎 (3房)
 $1461万
 $24,763/呎
-(26年-03月-03日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -39813,7 +39809,7 @@
           <t>C | 590呎 (3房)
 $1405万
 $23,814/呎
-(26年-04月-29日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -39828,15 +39824,15 @@
           <t>A | 1339呎 (4+房)
 $5657万
 $42,248/呎
-(25年-08月-18日)</t>
-        </is>
-      </c>
-      <c r="C23" s="23" t="inlineStr">
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 1171呎 (4+房)
-招标单位
--
-(在售)</t>
+$4790万
+$40,905/呎
+(26年-07月)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -39844,7 +39840,7 @@
           <t>C | 590呎 (3房)
 $1440万
 $24,410/呎
-(26年-03月-02日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -39859,7 +39855,7 @@
           <t>A | 1428呎 (4+房)
 $5614万
 $39,314/呎
-(23年-05月-28日)</t>
+(23年-05月)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -39867,7 +39863,7 @@
           <t>B | 1171呎 (4+房)
 $4763万
 $40,675/呎
-(26年-06月-15日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -39875,7 +39871,7 @@
           <t>C | 590呎 (3房)
 $1422万
 $24,108/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
     </row>
@@ -39890,7 +39886,7 @@
           <t>A | 1339呎 (4+房)
 $5468万
 $40,833/呎
-(24年-12月-02日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -39898,7 +39894,7 @@
           <t>B | 1171呎 (4+房)
 $4711万
 $40,231/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -39906,7 +39902,7 @@
           <t>C | 590呎 (3房)
 $1416万
 $24,001/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
     </row>
@@ -39921,7 +39917,7 @@
           <t>A | 1339呎 (4+房)
 $5558万
 $41,509/呎
-(25年-10月-13日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -39929,7 +39925,7 @@
           <t>B | 1171呎 (4+房)
 $4510万
 $38,514/呎
-(25年-11月-02日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -39937,7 +39933,7 @@
           <t>C | 590呎 (3房)
 $1410万
 $23,893/呎
-(26年-03月-08日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -39952,7 +39948,7 @@
           <t>A | 1339呎 (4+房)
 $5546万
 $41,419/呎
-(25年-11月-05日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -39960,7 +39956,7 @@
           <t>B | 1171呎 (4+房)
 $4493万
 $38,369/呎
-(25年-12月-10日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -39968,7 +39964,7 @@
           <t>C | 590呎 (3房)
 $1407万
 $23,839/呎
-(26年-03月-04日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -39983,7 +39979,7 @@
           <t>A | 1339呎 (4+房)
 $5365万
 $40,067/呎
-(25年-06月-11日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -39991,7 +39987,7 @@
           <t>B | 1171呎 (4+房)
 $4557万
 $38,915/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -39999,7 +39995,7 @@
           <t>C | 590呎 (3房)
 $1361万
 $23,072/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -40014,7 +40010,7 @@
           <t>A | 1339呎 (4+房)
 $5432万
 $40,568/呎
-(25年-11月-03日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -40022,7 +40018,7 @@
           <t>B | 1171呎 (4+房)
 $4408万
 $37,643/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -40030,7 +40026,7 @@
           <t>C | 590呎 (3房)
 $1397万
 $23,678/呎
-(26年-04月-08日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -40045,7 +40041,7 @@
           <t>A | 1339呎 (4+房)
 $5393万
 $40,275/呎
-(25年-07月-29日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -40053,7 +40049,7 @@
           <t>B | 1171呎 (4+房)
 $4379万
 $37,395/呎
-(25年-10月-15日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -40061,7 +40057,7 @@
           <t>C | 590呎 (3房)
 $1349万
 $22,864/呎
-(26年-04月-13日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -40076,7 +40072,7 @@
           <t>A | 1339呎 (4+房)
 $5327万
 $39,783/呎
-(26年-02月-25日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -40084,7 +40080,7 @@
           <t>B | 1171呎 (4+房)
 $4460万
 $38,087/呎
-(26年-02月-03日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -40092,7 +40088,7 @@
           <t>C | 590呎 (3房)
 $1324万
 $22,446/呎
-(26年-04月-12日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -40107,7 +40103,7 @@
           <t>A | 1339呎 (4+房)
 $5223万
 $39,007/呎
-(26年-04月-12日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -40115,7 +40111,7 @@
           <t>B | 1171呎 (4+房)
 $4412万
 $37,677/呎
-(26年-03月-02日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr"/>
@@ -40319,7 +40315,7 @@
           <t>B | 920呎 (3房)
 $3982万
 $43,283/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -40342,7 +40338,7 @@
           <t>B | 920呎 (3房)
 $3889万
 $42,272/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -40365,7 +40361,7 @@
           <t>B | 920呎 (3房)
 $3638万
 $39,543/呎
-(25年-11月-18日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -40388,7 +40384,7 @@
           <t>B | 920呎 (3房)
 $3610万
 $39,239/呎
-(25年-12月-21日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -40411,7 +40407,7 @@
           <t>B | 920呎 (3房)
 $3454万
 $37,543/呎
-(25年-03月-24日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -40426,7 +40422,7 @@
           <t>A | 1076呎 (4+房)
 $4590万
 $42,658/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -40434,7 +40430,7 @@
           <t>B | 1002呎 (3房)
 $3390万
 $33,832/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -40457,7 +40453,7 @@
           <t>B | 1002呎 (3房)
 $3345万
 $33,383/呎
-(24年-06月-25日)</t>
+(24年-06月)</t>
         </is>
       </c>
     </row>
@@ -40472,7 +40468,7 @@
           <t>A | 1173呎 (4+房)
 $4111万
 $35,047/呎
-(25年-06月-03日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -40480,7 +40476,7 @@
           <t>B | 1002呎 (3房)
 $3310万
 $33,034/呎
-(24年-05月-01日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -40495,7 +40491,7 @@
           <t>A | 1076呎 (4+房)
 $4388万
 $40,781/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -40503,7 +40499,7 @@
           <t>B | 920呎 (3房)
 $3306万
 $35,935/呎
-(24年-06月-03日)</t>
+(24年-06月)</t>
         </is>
       </c>
     </row>
@@ -40518,7 +40514,7 @@
           <t>A | 1076呎 (4+房)
 $4365万
 $40,567/呎
-(26年-04月-09日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -40526,7 +40522,7 @@
           <t>B | 1002呎 (3房)
 $3286万
 $32,794/呎
-(24年-05月-09日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -40541,7 +40537,7 @@
           <t>A | 1173呎 (4+房)
 $4100万
 $34,953/呎
-(23年-05月-30日)</t>
+(23年-05月)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -40549,7 +40545,7 @@
           <t>B | 1002呎 (3房)
 $3270万
 $32,635/呎
-(24年-07月-14日)</t>
+(24年-07月)</t>
         </is>
       </c>
     </row>
@@ -40564,7 +40560,7 @@
           <t>A | 1076呎 (4+房)
 $4038万
 $37,528/呎
-(25年-07月-03日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -40572,7 +40568,7 @@
           <t>B | 920呎 (3房)
 $3303万
 $35,902/呎
-(24年-11月-21日)</t>
+(24年-11月)</t>
         </is>
       </c>
     </row>
@@ -40587,7 +40583,7 @@
           <t>A | 1173呎 (4+房)
 $3990万
 $34,015/呎
-(24年-04月-22日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -40595,7 +40591,7 @@
           <t>B | 1002呎 (3房)
 $3228万
 $32,216/呎
-(24年-04月-22日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -40610,7 +40606,7 @@
           <t>A | 1173呎 (4+房)
 $3965万
 $33,802/呎
-(24年-03月-27日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -40618,7 +40614,7 @@
           <t>B | 1002呎 (3房)
 $3190万
 $31,836/呎
-(24年-04月-04日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -40633,7 +40629,7 @@
           <t>A | 1173呎 (4+房)
 $3921万
 $33,427/呎
-(23年-11月-09日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -40641,7 +40637,7 @@
           <t>B | 1002呎 (3房)
 $3157万
 $31,507/呎
-(23年-05月-18日)</t>
+(23年-05月)</t>
         </is>
       </c>
     </row>
@@ -40656,7 +40652,7 @@
           <t>A | 1173呎 (4+房)
 $3997万
 $34,075/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -40664,7 +40660,7 @@
           <t>B | 920呎 (3房)
 $3140万
 $34,130/呎
-(24年-03月-24日)</t>
+(24年-03月)</t>
         </is>
       </c>
     </row>
@@ -40679,7 +40675,7 @@
           <t>A | 1173呎 (4+房)
 $3972万
 $33,862/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -40687,7 +40683,7 @@
           <t>B | 920呎 (3房)
 $3219万
 $34,989/呎
-(25年-08月-26日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -40702,7 +40698,7 @@
           <t>A | 1173呎 (4+房)
 $3861万
 $32,917/呎
-(23年-11月-29日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -40710,7 +40706,7 @@
           <t>B | 1002呎 (3房)
 $3130万
 $31,238/呎
-(24年-05月-09日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -40725,7 +40721,7 @@
           <t>A | 1173呎 (4+房)
 $3910万
 $33,333/呎
-(23年-07月-19日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -40733,7 +40729,7 @@
           <t>B | 1002呎 (3房)
 $3093万
 $30,868/呎
-(24年-04月-18日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -40748,7 +40744,7 @@
           <t>A | 1076呎 (4+房)
 $3836万
 $35,651/呎
-(24年-04月-18日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -40756,7 +40752,7 @@
           <t>B | 1002呎 (3房)
 $3103万
 $30,968/呎
-(24年-05月-02日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -40771,7 +40767,7 @@
           <t>A | 1173呎 (4+房)
 $3854万
 $32,856/呎
-(23年-06月-01日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -40779,7 +40775,7 @@
           <t>B | 920呎 (3房)
 $3138万
 $34,109/呎
-(25年-09月-03日)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -40794,7 +40790,7 @@
           <t>A | 1173呎 (4+房)
 $3780万
 $32,225/呎
-(24年-05月-06日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -40802,7 +40798,7 @@
           <t>B | 920呎 (3房)
 $3044万
 $33,087/呎
-(24年-05月-06日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -40817,7 +40813,7 @@
           <t>A | 1076呎 (4+房)
 $3730万
 $34,667/呎
-(24年-06月-05日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -40825,7 +40821,7 @@
           <t>B | 920呎 (3房)
 $3032万
 $32,957/呎
-(24年-05月-20日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -40840,7 +40836,7 @@
           <t>A | 1076呎 (4+房)
 $3715万
 $34,526/呎
-(25年-03月-25日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -40848,7 +40844,7 @@
           <t>B | 920呎 (3房)
 $3028万
 $32,913/呎
-(25年-04月-01日)</t>
+(25年-04月)</t>
         </is>
       </c>
     </row>
@@ -40863,7 +40859,7 @@
           <t>A | 1076呎 (4+房)
 $3651万
 $33,931/呎
-(25年-05月-20日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -40871,7 +40867,7 @@
           <t>B | 1002呎 (3房)
 $2960万
 $29,541/呎
-(25年-03月-31日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -41009,7 +41005,7 @@
           <t>A | 1677呎 (4+房)
 $9203万
 $54,880/呎
-(23年-06月-27日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -41197,7 +41193,7 @@
           <t>A | 1102呎 (3房)
 $4042万
 $36,679/呎
-(24年-11月-18日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -41205,7 +41201,7 @@
           <t>B | 1085呎 (3房)
 $4002万
 $36,885/呎
-(24年-11月-21日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -41244,7 +41240,7 @@
           <t>B | 994呎 (3房)
 $4060万
 $40,845/呎
-(25年-12月-16日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -41283,7 +41279,7 @@
           <t>B | 994呎 (3房)
 $3860万
 $38,833/呎
-(25年-01月-14日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -41314,7 +41310,7 @@
           <t>A | 1102呎 (3房)
 $3774万
 $34,247/呎
-(24年-11月-21日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -41322,7 +41318,7 @@
           <t>B | 1085呎 (3房)
 $3774万
 $34,783/呎
-(24年-12月-02日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -41353,7 +41349,7 @@
           <t>A | 1102呎 (3房)
 $3708万
 $33,648/呎
-(24年-05月-16日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -41361,7 +41357,7 @@
           <t>B | 994呎 (3房)
 $3752万
 $37,746/呎
-(25年-01月-09日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -41392,7 +41388,7 @@
           <t>A | 1027呎 (3房)
 $3680万
 $35,833/呎
-(24年-04月-28日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -41400,7 +41396,7 @@
           <t>B | 994呎 (3房)
 $3660万
 $36,821/呎
-(24年-04月-28日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -41431,7 +41427,7 @@
           <t>A | 1102呎 (3房)
 $3671万
 $33,312/呎
-(24年-12月-02日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -41439,7 +41435,7 @@
           <t>B | 1085呎 (3房)
 $3672万
 $33,843/呎
-(24年-12月-02日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -41470,7 +41466,7 @@
           <t>A | 1027呎 (3房)
 $4114万
 $40,057/呎
-(26年-04月-29日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -41478,7 +41474,7 @@
           <t>B | 994呎 (3房)
 $4960万
 $49,899/呎
-(26年-06月-23日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -41509,7 +41505,7 @@
           <t>A | 1102呎 (3房)
 $3700万
 $33,575/呎
-(24年-04月-04日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -41517,7 +41513,7 @@
           <t>B | 994呎 (3房)
 $3629万
 $36,509/呎
-(24年-12月-05日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -41548,7 +41544,7 @@
           <t>A | 1102呎 (3房)
 $3627万
 $32,913/呎
-(24年-11月-21日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -41556,7 +41552,7 @@
           <t>B | 1085呎 (3房)
 $3627万
 $33,428/呎
-(24年-11月-21日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -41587,7 +41583,7 @@
           <t>A | 1027呎 (3房)
 $3584万
 $34,898/呎
-(24年-12月-02日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -41595,7 +41591,7 @@
           <t>B | 1085呎 (3房)
 $3584万
 $33,032/呎
-(24年-12月-05日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -41626,7 +41622,7 @@
           <t>A | 1027呎 (3房)
 $3563万
 $34,693/呎
-(24年-11月-18日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -41634,7 +41630,7 @@
           <t>B | 1085呎 (3房)
 $3562万
 $32,832/呎
-(24年-11月-21日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -41665,7 +41661,7 @@
           <t>A | 1027呎 (3房)
 $3593万
 $34,985/呎
-(25年-09月-17日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -41673,7 +41669,7 @@
           <t>B | 994呎 (3房)
 $3540万
 $35,611/呎
-(24年-11月-21日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -41704,7 +41700,7 @@
           <t>A | 1102呎 (3房)
 $3520万
 $31,942/呎
-(24年-12月-05日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -41712,7 +41708,7 @@
           <t>B | 1085呎 (3房)
 $3518万
 $32,426/呎
-(24年-11月-21日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -41743,7 +41739,7 @@
           <t>A | 1102呎 (3房)
 $3497万
 $31,730/呎
-(24年-11月-18日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -41751,7 +41747,7 @@
           <t>B | 1085呎 (3房)
 $3497万
 $32,228/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -41782,7 +41778,7 @@
           <t>A | 1027呎 (3房)
 $3880万
 $37,780/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -41790,7 +41786,7 @@
           <t>B | 994呎 (3房)
 $3555万
 $35,765/呎
-(24年-12月-03日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -41821,7 +41817,7 @@
           <t>A | 1102呎 (3房)
 $3454万
 $31,338/呎
-(24年-12月-02日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -41829,7 +41825,7 @@
           <t>B | 994呎 (3房)
 $3454万
 $34,744/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -41860,7 +41856,7 @@
           <t>A | 1102呎 (3房)
 $3464万
 $31,434/呎
-(24年-12月-05日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -41868,7 +41864,7 @@
           <t>B | 1085呎 (3房)
 $3524万
 $32,479/呎
-(24年-11月-18日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -41899,7 +41895,7 @@
           <t>A | 1102呎 (3房)
 $3428万
 $31,107/呎
-(24年-12月-15日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -41907,7 +41903,7 @@
           <t>B | 1085呎 (3房)
 $3450万
 $31,797/呎
-(24年-12月-15日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -41938,7 +41934,7 @@
           <t>A | 1102呎 (3房)
 $3388万
 $30,744/呎
-(24年-11月-21日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -41946,7 +41942,7 @@
           <t>B | 1085呎 (3房)
 $3388万
 $31,226/呎
-(24年-11月-21日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -41977,7 +41973,7 @@
           <t>A | 1102呎 (3房)
 $3357万
 $30,463/呎
-(24年-12月-02日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -41985,7 +41981,7 @@
           <t>B | 994呎 (3房)
 $3351万
 $33,712/呎
-(24年-12月-05日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -42016,7 +42012,7 @@
           <t>A | 1027呎 (3房)
 $3323万
 $32,356/呎
-(25年-04月-07日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -42024,7 +42020,7 @@
           <t>B | 1085呎 (3房)
 $3290万
 $30,323/呎
-(25年-02月-27日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -42055,7 +42051,7 @@
           <t>A | 1102呎 (3房)
 $3258万
 $29,564/呎
-(24年-12月-15日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -42063,7 +42059,7 @@
           <t>B | 994呎 (3房)
 $3530万
 $35,513/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -42305,7 +42301,7 @@
           <t>B | 1282呎 (4+房)
 $6036万
 $47,083/呎
-(26年-07月-16日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -42328,7 +42324,7 @@
           <t>B | 1282呎 (4+房)
 $5982万
 $46,661/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
     </row>
@@ -42343,7 +42339,7 @@
           <t>A | 1282呎 (4+房)
 $5591万
 $43,612/呎
-(25年-11月-26日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -42351,7 +42347,7 @@
           <t>B | 1382呎 (4+房)
 $5390万
 $39,001/呎
-(23年-06月-08日)</t>
+(23年-06月)</t>
         </is>
       </c>
     </row>
@@ -42366,7 +42362,7 @@
           <t>A | 1382呎 (4+房)
 $5373万
 $38,878/呎
-(25年-02月-19日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -42374,7 +42370,7 @@
           <t>B | 1382呎 (4+房)
 $5373万
 $38,878/呎
-(25年-02月-19日)</t>
+(25年-02月)</t>
         </is>
       </c>
     </row>
@@ -42397,7 +42393,7 @@
           <t>B | 1282呎 (4+房)
 $5432万
 $42,371/呎
-(25年-09月-09日)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -42412,7 +42408,7 @@
           <t>A | 1382呎 (4+房)
 $5380万
 $38,929/呎
-(23年-06月-07日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -42420,7 +42416,7 @@
           <t>B | 1382呎 (4+房)
 $5380万
 $38,929/呎
-(23年-06月-07日)</t>
+(23年-06月)</t>
         </is>
       </c>
     </row>
@@ -42435,7 +42431,7 @@
           <t>A | 1382呎 (4+房)
 $5227万
 $37,822/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -42443,7 +42439,7 @@
           <t>B | 1282呎 (4+房)
 $5226万
 $40,767/呎
-(24年-12月-10日)</t>
+(24年-12月)</t>
         </is>
       </c>
     </row>
@@ -42458,7 +42454,7 @@
           <t>A | 1282呎 (4+房)
 $5195万
 $40,523/呎
-(25年-05月-05日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -42466,7 +42462,7 @@
           <t>B | 1282呎 (4+房)
 $5195万
 $40,523/呎
-(25年-06月-05日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -42481,7 +42477,7 @@
           <t>A | 1382呎 (4+房)
 $5165万
 $37,370/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -42489,7 +42485,7 @@
           <t>B | 1382呎 (4+房)
 $5145万
 $37,229/呎
-(24年-04月-08日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -42504,7 +42500,7 @@
           <t>A | 1282呎 (4+房)
 $5246万
 $40,919/呎
-(25年-11月-04日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -42512,7 +42508,7 @@
           <t>B | 1382呎 (4+房)
 $5134万
 $37,151/呎
-(24年-11月-20日)</t>
+(24年-11月)</t>
         </is>
       </c>
     </row>
@@ -42527,7 +42523,7 @@
           <t>A | 1282呎 (4+房)
 $5428万
 $42,340/呎
-(26年-02月-23日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -42535,7 +42531,7 @@
           <t>B | 1382呎 (4+房)
 $5134万
 $37,149/呎
-(24年-11月-25日)</t>
+(24年-11月)</t>
         </is>
       </c>
     </row>
@@ -42550,7 +42546,7 @@
           <t>A | 1382呎 (4+房)
 $5080万
 $36,758/呎
-(25年-06月-03日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -42558,7 +42554,7 @@
           <t>B | 1382呎 (4+房)
 $5080万
 $36,758/呎
-(25年-06月-03日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -42573,7 +42569,7 @@
           <t>A | 1382呎 (4+房)
 $5043万
 $36,491/呎
-(24年-04月-23日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -42581,7 +42577,7 @@
           <t>B | 1382呎 (4+房)
 $5042万
 $36,484/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
     </row>
@@ -42596,7 +42592,7 @@
           <t>A | 1282呎 (4+房)
 $5070万
 $39,548/呎
-(25年-08月-19日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -42604,7 +42600,7 @@
           <t>B | 1282呎 (4+房)
 $5070万
 $39,548/呎
-(25年-08月-31日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -42619,7 +42615,7 @@
           <t>A | 1282呎 (4+房)
 $4981万
 $38,853/呎
-(25年-04月-23日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -42627,7 +42623,7 @@
           <t>B | 1282呎 (4+房)
 $5060万
 $39,470/呎
-(25年-08月-10日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -42642,7 +42638,7 @@
           <t>A | 1282呎 (4+房)
 $5050万
 $39,392/呎
-(25年-11月-24日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -42650,7 +42646,7 @@
           <t>B | 1282呎 (4+房)
 $5050万
 $39,392/呎
-(25年-10月-12日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -42665,7 +42661,7 @@
           <t>A | 1282呎 (4+房)
 $4898万
 $38,206/呎
-(25年-05月-07日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -42673,7 +42669,7 @@
           <t>B | 1282呎 (4+房)
 $4898万
 $38,206/呎
-(25年-05月-07日)</t>
+(25年-05月)</t>
         </is>
       </c>
     </row>
@@ -42688,7 +42684,7 @@
           <t>A | 1282呎 (4+房)
 $4995万
 $38,963/呎
-(25年-10月-16日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -42696,7 +42692,7 @@
           <t>B | 1382呎 (4+房)
 $4888万
 $35,371/呎
-(24年-11月-27日)</t>
+(24年-11月)</t>
         </is>
       </c>
     </row>
@@ -42711,7 +42707,7 @@
           <t>A | 1282呎 (4+房)
 $4966万
 $38,736/呎
-(25年-10月-13日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -42719,7 +42715,7 @@
           <t>B | 1282呎 (4+房)
 $4966万
 $38,736/呎
-(25年-10月-13日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -42734,7 +42730,7 @@
           <t>A | 1282呎 (4+房)
 $4908万
 $38,284/呎
-(25年-10月-29日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -42742,7 +42738,7 @@
           <t>B | 1282呎 (4+房)
 $4908万
 $38,284/呎
-(25年-10月-29日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -42757,7 +42753,7 @@
           <t>A | 1282呎 (4+房)
 $4814万
 $37,549/呎
-(25年-10月-16日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -42765,7 +42761,7 @@
           <t>B | 1282呎 (4+房)
 $4819万
 $37,590/呎
-(25年-11月-11日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -42780,7 +42776,7 @@
           <t>A | 1282呎 (4+房)
 $4845万
 $37,793/呎
-(25年-11月-24日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -42788,7 +42784,7 @@
           <t>B | 1282呎 (4+房)
 $4961万
 $38,697/呎
-(25年-12月-23日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -42803,7 +42799,7 @@
           <t>A | 1282呎 (4+房)
 $4882万
 $38,081/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -42811,7 +42807,7 @@
           <t>B | 1282呎 (4+房)
 $4753万
 $37,075/呎
-(25年-11月-03日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -42826,7 +42822,7 @@
           <t>A | 1282呎 (4+房)
 $4868万
 $37,972/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -42834,7 +42830,7 @@
           <t>B | 1282呎 (4+房)
 $4877万
 $38,042/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -43199,7 +43195,7 @@
           <t>A | 992呎 (3房)
 $4469万
 $45,050/呎
-(26年-06月-29日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -43207,7 +43203,7 @@
           <t>B | 1027呎 (3房)
 $4518万
 $43,992/呎
-(26年-06月-29日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -43238,7 +43234,7 @@
           <t>A | 992呎 (3房)
 $4405万
 $44,405/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -43277,7 +43273,7 @@
           <t>A | 992呎 (3房)
 $4341万
 $43,760/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -43285,7 +43281,7 @@
           <t>B | 1027呎 (3房)
 $4427万
 $43,106/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -43316,7 +43312,7 @@
           <t>A | 992呎 (3房)
 $4217万
 $42,510/呎
-(26年-02月-24日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -43355,7 +43351,7 @@
           <t>A | 992呎 (3房)
 $3865万
 $38,962/呎
-(25年-09月-15日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -43363,7 +43359,7 @@
           <t>B | 1027呎 (3房)
 $4300万
 $41,870/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -43394,7 +43390,7 @@
           <t>A | 992呎 (3房)
 $3843万
 $38,740/呎
-(25年-10月-23日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -43402,7 +43398,7 @@
           <t>B | 1027呎 (3房)
 $3885万
 $37,829/呎
-(25年-10月-23日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -43433,7 +43429,7 @@
           <t>A | 992呎 (3房)
 $3898万
 $39,294/呎
-(25年-11月-24日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -43441,7 +43437,7 @@
           <t>B | 1027呎 (3房)
 $4129万
 $40,204/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -43472,7 +43468,7 @@
           <t>A | 992呎 (3房)
 $3820万
 $38,508/呎
-(25年-10月-12日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -43480,7 +43476,7 @@
           <t>B | 1027呎 (3房)
 $3935万
 $38,315/呎
-(25年-12月-09日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -43511,7 +43507,7 @@
           <t>A | 992呎 (3房)
 $3818万
 $38,488/呎
-(25年-11月-09日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -43519,7 +43515,7 @@
           <t>B | 1027呎 (3房)
 $3878万
 $37,760/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -43589,7 +43585,7 @@
           <t>A | 992呎 (3房)
 $3740万
 $37,702/呎
-(25年-10月-13日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -43597,7 +43593,7 @@
           <t>B | 1027呎 (3房)
 $3780万
 $36,806/呎
-(25年-09月-09日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -43628,7 +43624,7 @@
           <t>A | 992呎 (3房)
 $3730万
 $37,601/呎
-(25年-10月-09日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -43636,7 +43632,7 @@
           <t>B | 1027呎 (3房)
 $3700万
 $36,027/呎
-(25年-07月-13日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -43667,7 +43663,7 @@
           <t>A | 992呎 (3房)
 $3679万
 $37,087/呎
-(25年-06月-26日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -43675,7 +43671,7 @@
           <t>B | 1027呎 (3房)
 $3728万
 $36,300/呎
-(25年-07月-13日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -43706,7 +43702,7 @@
           <t>A | 992呎 (3房)
 $3600万
 $36,290/呎
-(25年-06月-12日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -43714,7 +43710,7 @@
           <t>B | 1027呎 (3房)
 $3640万
 $35,443/呎
-(25年-05月-05日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -43745,7 +43741,7 @@
           <t>A | 1085呎 (3房)
 $3587万
 $33,060/呎
-(25年-06月-16日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -43753,7 +43749,7 @@
           <t>B | 1102呎 (3房)
 $3618万
 $32,831/呎
-(25年-07月-06日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -43784,7 +43780,7 @@
           <t>A | 992呎 (3房)
 $3565万
 $35,938/呎
-(25年-04月-24日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -43792,7 +43788,7 @@
           <t>B | 1102呎 (3房)
 $3603万
 $32,695/呎
-(25年-05月-20日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -43823,7 +43819,7 @@
           <t>A | 992呎 (3房)
 $3626万
 $36,552/呎
-(25年-08月-19日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -43831,7 +43827,7 @@
           <t>B | 1027呎 (3房)
 $3664万
 $35,677/呎
-(25年-08月-19日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -43862,7 +43858,7 @@
           <t>A | 992呎 (3房)
 $3453万
 $34,808/呎
-(25年-05月-26日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -43870,7 +43866,7 @@
           <t>B | 1027呎 (3房)
 $3653万
 $35,570/呎
-(25年-09月-01日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -43901,7 +43897,7 @@
           <t>A | 992呎 (3房)
 $3274万
 $33,004/呎
-(25年-04月-07日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -43909,7 +43905,7 @@
           <t>B | 1042呎 (3房)
 $3771万
 $36,190/呎
-(26年-04月-29日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -43940,7 +43936,7 @@
           <t>A | 1085呎 (3房)
 $3230万
 $29,770/呎
-(25年-04月-16日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -43948,7 +43944,7 @@
           <t>B | 1042呎 (3房)
 $3193万
 $30,643/呎
-(25年-04月-16日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -43979,7 +43975,7 @@
           <t>A | 992呎 (3房)
 $3184万
 $32,097/呎
-(25年-04月-07日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -44018,7 +44014,7 @@
           <t>A | 1085呎 (3房)
 $3127万
 $28,820/呎
-(25年-05月-13日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">
@@ -44260,7 +44256,7 @@
           <t>A | 920呎 (3房)
 $4111万
 $44,685/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -44283,7 +44279,7 @@
           <t>A | 920呎 (3房)
 $3835万
 $41,685/呎
-(26年-01月-22日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -44291,7 +44287,7 @@
           <t>B | 1076呎 (4+房)
 $4636万
 $43,086/呎
-(26年-01月-22日)</t>
+(26年-01月)</t>
         </is>
       </c>
     </row>
@@ -44306,7 +44302,7 @@
           <t>A | 920呎 (3房)
 $3675万
 $39,946/呎
-(25年-11月-03日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -44314,7 +44310,7 @@
           <t>B | 1076呎 (4+房)
 $4430万
 $41,171/呎
-(25年-11月-03日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -44329,7 +44325,7 @@
           <t>A | 920呎 (3房)
 $3643万
 $39,598/呎
-(25年-10月-14日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -44337,7 +44333,7 @@
           <t>B | 1076呎 (4+房)
 $4405万
 $40,939/呎
-(25年-10月-14日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -44352,7 +44348,7 @@
           <t>A | 1002呎 (3房)
 $3613万
 $36,058/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -44360,7 +44356,7 @@
           <t>B | 1173呎 (4+房)
 $4370万
 $37,255/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -44375,7 +44371,7 @@
           <t>A | 920呎 (3房)
 $3580万
 $38,913/呎
-(25年-08月-05日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -44383,7 +44379,7 @@
           <t>B | 1076呎 (4+房)
 $4345万
 $40,381/呎
-(25年-08月-17日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -44398,7 +44394,7 @@
           <t>A | 920呎 (3房)
 $3534万
 $38,413/呎
-(25年-07月-23日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -44406,7 +44402,7 @@
           <t>B | 1076呎 (4+房)
 $4298万
 $39,944/呎
-(25年-11月-05日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -44421,7 +44417,7 @@
           <t>A | 920呎 (3房)
 $3472万
 $37,739/呎
-(25年-06月-09日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -44429,7 +44425,7 @@
           <t>B | 1173呎 (4+房)
 $4214万
 $35,925/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -44444,7 +44440,7 @@
           <t>A | 920呎 (3房)
 $3513万
 $38,185/呎
-(25年-08月-26日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -44452,7 +44448,7 @@
           <t>B | 1076呎 (4+房)
 $4246万
 $39,461/呎
-(25年-08月-26日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -44467,7 +44463,7 @@
           <t>A | 920呎 (3房)
 $3498万
 $38,022/呎
-(25年-08月-26日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -44475,7 +44471,7 @@
           <t>B | 1076呎 (4+房)
 $4228万
 $39,294/呎
-(25年-07月-24日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -44490,7 +44486,7 @@
           <t>A | 920呎 (3房)
 $3421万
 $37,185/呎
-(25年-04月-14日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -44498,7 +44494,7 @@
           <t>B | 1173呎 (4+房)
 $4140万
 $35,294/呎
-(25年-01月-27日)</t>
+(25年-01月)</t>
         </is>
       </c>
     </row>
@@ -44513,7 +44509,7 @@
           <t>A | 1002呎 (3房)
 $3395万
 $33,882/呎
-(25年-07月-02日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -44521,7 +44517,7 @@
           <t>B | 1076呎 (4+房)
 $4188万
 $38,922/呎
-(25年-10月-23日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -44536,7 +44532,7 @@
           <t>A | 920呎 (3房)
 $3380万
 $36,739/呎
-(25年-06月-05日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -44544,7 +44540,7 @@
           <t>B | 1076呎 (4+房)
 $4090万
 $38,011/呎
-(25年-05月-27日)</t>
+(25年-05月)</t>
         </is>
       </c>
     </row>
@@ -44559,7 +44555,7 @@
           <t>A | 920呎 (3房)
 $3359万
 $36,511/呎
-(25年-04月-29日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -44567,7 +44563,7 @@
           <t>B | 1173呎 (4+房)
 $4066万
 $34,663/呎
-(24年-12月-03日)</t>
+(24年-12月)</t>
         </is>
       </c>
     </row>
@@ -44582,7 +44578,7 @@
           <t>A | 920呎 (3房)
 $3330万
 $36,196/呎
-(24年-12月-30日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -44590,7 +44586,7 @@
           <t>B | 1076呎 (4+房)
 $4037万
 $37,519/呎
-(25年-06月-04日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -44605,7 +44601,7 @@
           <t>A | 920呎 (3房)
 $3318万
 $36,065/呎
-(24年-12月-19日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -44613,7 +44609,7 @@
           <t>B | 1173呎 (4+房)
 $4016万
 $34,237/呎
-(25年-05月-15日)</t>
+(25年-05月)</t>
         </is>
       </c>
     </row>
@@ -44628,7 +44624,7 @@
           <t>A | 1002呎 (3房)
 $3290万
 $32,834/呎
-(25年-01月-15日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -44636,7 +44632,7 @@
           <t>B | 1076呎 (3房)
 $4087万
 $37,983/呎
-(25年-10月-13日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -44651,7 +44647,7 @@
           <t>A | 920呎 (3房)
 $3271万
 $35,554/呎
-(25年-04月-29日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -44659,7 +44655,7 @@
           <t>B | 1076呎 (4+房)
 $3958万
 $36,784/呎
-(25年-06月-03日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -44674,7 +44670,7 @@
           <t>A | 920呎 (3房)
 $3295万
 $35,815/呎
-(25年-09月-03日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -44682,7 +44678,7 @@
           <t>B | 1076呎 (4+房)
 $3988万
 $37,063/呎
-(25年-10月-13日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -44697,7 +44693,7 @@
           <t>A | 920呎 (3房)
 $3416万
 $37,130/呎
-(25年-12月-16日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -44705,7 +44701,7 @@
           <t>B | 1076呎 (4+房)
 $4058万
 $37,714/呎
-(26年-07月-07日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -44843,7 +44839,7 @@
           <t>A | 1890呎 (4+房)
 $10395万
 $55,000/呎
-(23年-06月-07日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -45039,7 +45035,7 @@
           <t>B | 1298呎 (4+房)
 $5013万
 $38,621/呎
-(24年-04月-04日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -45070,7 +45066,7 @@
           <t>A | 1165呎 (4+房)
 $5381万
 $46,189/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -45117,7 +45113,7 @@
           <t>B | 1298呎 (4+房)
 $4936万
 $38,028/呎
-(24年-04月-24日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -45148,7 +45144,7 @@
           <t>A | 1165呎 (4+房)
 $4898万
 $42,043/呎
-(25年-09月-21日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -45226,7 +45222,7 @@
           <t>A | 1259呎 (4+房)
 $4712万
 $37,426/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -45234,7 +45230,7 @@
           <t>B | 1298呎 (4+房)
 $4808万
 $37,042/呎
-(24年-05月-02日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -45265,7 +45261,7 @@
           <t>A | 1259呎 (4+房)
 $4663万
 $37,037/呎
-(24年-04月-28日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -45273,7 +45269,7 @@
           <t>B | 1298呎 (4+房)
 $4771万
 $36,757/呎
-(24年-04月-29日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -45304,7 +45300,7 @@
           <t>A | 1165呎 (4+房)
 $4988万
 $42,815/呎
-(26年-02月-03日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -45312,7 +45308,7 @@
           <t>B | 1204呎 (4+房)
 $5103万
 $42,384/呎
-(26年-02月-03日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -45351,7 +45347,7 @@
           <t>B | 1298呎 (4+房)
 $4765万
 $36,710/呎
-(24年-04月-04日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -45390,7 +45386,7 @@
           <t>B | 1298呎 (4+房)
 $4688万
 $36,117/呎
-(24年-04月-18日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -45421,7 +45417,7 @@
           <t>A | 1165呎 (4+房)
 $4800万
 $41,202/呎
-(26年-03月-22日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -45429,7 +45425,7 @@
           <t>B | 1298呎 (4+房)
 $4657万
 $35,878/呎
-(23年-06月-06日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -45499,7 +45495,7 @@
           <t>A | 1165呎 (4+房)
 $4750万
 $40,773/呎
-(26年-02月-09日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -45507,7 +45503,7 @@
           <t>B | 1204呎 (4+房)
 $5153万
 $42,799/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -45538,7 +45534,7 @@
           <t>A | 1165呎 (4+房)
 $4548万
 $39,039/呎
-(25年-09月-15日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -45546,7 +45542,7 @@
           <t>B | 1298呎 (4+房)
 $4646万
 $35,794/呎
-(25年-07月-21日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -45577,7 +45573,7 @@
           <t>A | 1165呎 (4+房)
 $4930万
 $42,318/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -45585,7 +45581,7 @@
           <t>B | 1204呎 (4+房)
 $4977万
 $41,337/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -45616,7 +45612,7 @@
           <t>A | 1165呎 (4+房)
 $4550万
 $39,056/呎
-(26年-02月-22日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -45624,7 +45620,7 @@
           <t>B | 1204呎 (4+房)
 $4900万
 $40,698/呎
-(26年-07月-08日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -45655,7 +45651,7 @@
           <t>A | 1165呎 (4+房)
 $4520万
 $38,798/呎
-(26年-01月-26日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -45889,7 +45885,7 @@
           <t>A | 908呎 (3房)
 $3904万
 $43,000/呎
-(23年-06月-27日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -45906,7 +45902,7 @@
           <t>A | 900呎 (3房)
 $3199万
 $35,544/呎
-(23年-07月-31日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -45914,7 +45910,7 @@
           <t>B | 836呎 (3房)
 $2949万
 $35,280/呎
-(24年-03月-20日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -45922,7 +45918,7 @@
           <t>C | 907呎 (3房)
 $3127万
 $34,472/呎
-(24年-04月-02日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -45937,7 +45933,7 @@
           <t>A | 900呎 (3房)
 $3397万
 $37,750/呎
-(23年-07月-17日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -45945,7 +45941,7 @@
           <t>B | 836呎 (3房)
 $2680万
 $32,060/呎
-(23年-07月-17日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -45953,7 +45949,7 @@
           <t>C | 907呎 (3房)
 $2916万
 $32,151/呎
-(23年-07月-17日)</t>
+(23年-07月)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-启德-天泷.xlsx
+++ b/files/九龙-启德-天泷.xlsx
@@ -27,7 +27,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -143,6 +143,11 @@
       <color rgb="00000000"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -220,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -292,6 +297,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3607,7 +3615,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -3617,12 +3625,12 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -3632,12 +3640,12 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
@@ -3647,7 +3655,7 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -11189,7 +11197,7 @@
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
@@ -11199,12 +11207,12 @@
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I158" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J158" s="3" t="inlineStr">
@@ -11214,12 +11222,12 @@
       </c>
       <c r="K158" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L158" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M158" s="3" t="inlineStr">
@@ -11229,7 +11237,7 @@
       </c>
       <c r="N158" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -11259,7 +11267,7 @@
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
@@ -11269,12 +11277,12 @@
       </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I159" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J159" s="3" t="inlineStr">
@@ -11284,12 +11292,12 @@
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L159" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M159" s="3" t="inlineStr">
@@ -11299,7 +11307,7 @@
       </c>
       <c r="N159" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -18013,7 +18021,7 @@
       </c>
       <c r="F258" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G258" s="3" t="inlineStr">
@@ -18023,12 +18031,12 @@
       </c>
       <c r="H258" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I258" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J258" s="3" t="inlineStr">
@@ -18038,12 +18046,12 @@
       </c>
       <c r="K258" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L258" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M258" s="3" t="inlineStr">
@@ -18053,7 +18061,7 @@
       </c>
       <c r="N258" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -18083,7 +18091,7 @@
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G259" s="3" t="inlineStr">
@@ -18093,12 +18101,12 @@
       </c>
       <c r="H259" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I259" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J259" s="3" t="inlineStr">
@@ -18108,12 +18116,12 @@
       </c>
       <c r="K259" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L259" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M259" s="3" t="inlineStr">
@@ -18123,7 +18131,7 @@
       </c>
       <c r="N259" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -23903,7 +23911,7 @@
       </c>
       <c r="F345" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G345" s="3" t="inlineStr">
@@ -23913,12 +23921,12 @@
       </c>
       <c r="H345" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I345" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J345" s="3" t="inlineStr">
@@ -23928,12 +23936,12 @@
       </c>
       <c r="K345" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L345" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M345" s="3" t="inlineStr">
@@ -23943,7 +23951,7 @@
       </c>
       <c r="N345" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -28539,7 +28547,7 @@
       </c>
       <c r="F413" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G413" s="3" t="inlineStr">
@@ -28549,12 +28557,12 @@
       </c>
       <c r="H413" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I413" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J413" s="3" t="inlineStr">
@@ -28564,12 +28572,12 @@
       </c>
       <c r="K413" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L413" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M413" s="3" t="inlineStr">
@@ -28579,7 +28587,7 @@
       </c>
       <c r="N413" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -38289,7 +38297,7 @@
       </c>
       <c r="F556" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G556" s="3" t="inlineStr">
@@ -38299,12 +38307,12 @@
       </c>
       <c r="H556" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I556" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J556" s="3" t="inlineStr">
@@ -38314,12 +38322,12 @@
       </c>
       <c r="K556" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L556" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M556" s="3" t="inlineStr">
@@ -38329,7 +38337,7 @@
       </c>
       <c r="N556" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -38639,7 +38647,7 @@
       </c>
       <c r="F561" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G561" s="3" t="inlineStr">
@@ -38649,12 +38657,12 @@
       </c>
       <c r="H561" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I561" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J561" s="3" t="inlineStr">
@@ -38664,12 +38672,12 @@
       </c>
       <c r="K561" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L561" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M561" s="3" t="inlineStr">
@@ -38679,7 +38687,7 @@
       </c>
       <c r="N561" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -39221,7 +39229,7 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -39236,7 +39244,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -39273,7 +39281,7 @@
           <t>A | 1942呎 (4+房)
 $11215万
 $57,750/呎
-(23年-06月)</t>
+(23年-06月-13日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -39313,7 +39321,7 @@
           <t>C | 590呎 (3房)
 $1617万
 $27,399/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -39344,7 +39352,7 @@
           <t>C | 590呎 (3房)
 $1568万
 $26,576/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
     </row>
@@ -39375,7 +39383,7 @@
           <t>C | 590呎 (3房)
 $1588万
 $26,907/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
     </row>
@@ -39406,7 +39414,7 @@
           <t>C | 590呎 (3房)
 $1540万
 $26,099/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
     </row>
@@ -39421,7 +39429,7 @@
           <t>A | 1339呎 (4+房)
 $6740万
 $50,336/呎
-(26年-06月)</t>
+(26年-06月-28日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -39437,7 +39445,7 @@
           <t>C | 590呎 (3房)
 $1575万
 $26,692/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
     </row>
@@ -39452,7 +39460,7 @@
           <t>A | 1339呎 (4+房)
 $6665万
 $49,776/呎
-(26年-06月)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -39468,7 +39476,7 @@
           <t>C | 590呎 (3房)
 $1568万
 $26,584/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
     </row>
@@ -39483,7 +39491,7 @@
           <t>A | 1339呎 (4+房)
 $6007万
 $44,862/呎
-(25年-06月)</t>
+(25年-06月-03日)</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
@@ -39499,7 +39507,7 @@
           <t>C | 590呎 (3房)
 $1562万
 $26,476/呎
-(26年-03月)</t>
+(26年-03月-18日)</t>
         </is>
       </c>
     </row>
@@ -39514,7 +39522,7 @@
           <t>A | 1339呎 (4+房)
 $6453万
 $48,193/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -39522,7 +39530,7 @@
           <t>B | 1171呎 (4+房)
 $5285万
 $45,132/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -39530,7 +39538,7 @@
           <t>C | 590呎 (3房)
 $1509万
 $25,577/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
     </row>
@@ -39545,7 +39553,7 @@
           <t>A | 1428呎 (4+房)
 $5860万
 $41,036/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -39553,7 +39561,7 @@
           <t>B | 1171呎 (4+房)
 $4868万
 $41,571/呎
-(25年-10月)</t>
+(25年-10月-20日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -39561,7 +39569,7 @@
           <t>C | 590呎 (3房)
 $1497万
 $25,369/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
     </row>
@@ -39576,7 +39584,7 @@
           <t>A | 1339呎 (4+房)
 $5810万
 $43,391/呎
-(25年-06月)</t>
+(25年-06月-03日)</t>
         </is>
       </c>
       <c r="C15" s="24" t="inlineStr">
@@ -39592,7 +39600,7 @@
           <t>C | 590呎 (3房)
 $1537万
 $26,046/呎
-(26年-03月)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
     </row>
@@ -39607,7 +39615,7 @@
           <t>A | 1339呎 (4+房)
 $6161万
 $46,012/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -39615,7 +39623,7 @@
           <t>B | 1171呎 (4+房)
 $4900万
 $41,845/呎
-(26年-02月)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -39623,7 +39631,7 @@
           <t>C | 590呎 (3房)
 $1491万
 $25,264/呎
-(26年-03月)</t>
+(26年-03月-12日)</t>
         </is>
       </c>
     </row>
@@ -39638,7 +39646,7 @@
           <t>A | 1428呎 (4+房)
 $5733万
 $40,146/呎
-(25年-01月)</t>
+(25年-01月-05日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -39646,7 +39654,7 @@
           <t>B | 1171呎 (4+房)
 $4756万
 $40,615/呎
-(25年-11月)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -39654,7 +39662,7 @@
           <t>C | 590呎 (3房)
 $1524万
 $25,831/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
     </row>
@@ -39669,7 +39677,7 @@
           <t>A | 1339呎 (3房)
 $5832万
 $43,555/呎
-(25年-12月)</t>
+(25年-12月-30日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -39677,7 +39685,7 @@
           <t>B | 1171呎 (4+房)
 $4719万
 $40,299/呎
-(25年-12月)</t>
+(25年-12月-30日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -39685,7 +39693,7 @@
           <t>C | 590呎 (3房)
 $1465万
 $24,825/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
     </row>
@@ -39700,15 +39708,15 @@
           <t>A | 1339呎 (4+房)
 $5976万
 $44,630/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C19" s="22" t="inlineStr">
+(26年-03月-29日)</t>
+        </is>
+      </c>
+      <c r="C19" s="25" t="inlineStr">
         <is>
           <t>B | 1258呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(已定价未售)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -39716,7 +39724,7 @@
           <t>C | 590呎 (3房)
 $1511万
 $25,615/呎
-(26年-03月)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
     </row>
@@ -39731,7 +39739,7 @@
           <t>A | 1428呎 (4+房)
 $5633万
 $39,447/呎
-(25年-06月)</t>
+(25年-06月-03日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -39739,7 +39747,7 @@
           <t>B | 1171呎 (4+房)
 $4568万
 $39,009/呎
-(25年-06月)</t>
+(25年-06月-08日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -39747,7 +39755,7 @@
           <t>C | 590呎 (3房)
 $1486万
 $25,185/呎
-(26年-03月)</t>
+(26年-03月-01日)</t>
         </is>
       </c>
     </row>
@@ -39762,7 +39770,7 @@
           <t>A | 1339呎 (4+房)
 $5550万
 $41,449/呎
-(25年-05月)</t>
+(25年-05月-13日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -39770,7 +39778,7 @@
           <t>B | 1171呎 (4+房)
 $4502万
 $38,446/呎
-(25年-05月)</t>
+(25年-05月-13日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -39778,7 +39786,7 @@
           <t>C | 590呎 (3房)
 $1461万
 $24,763/呎
-(26年-03月)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
     </row>
@@ -39809,7 +39817,7 @@
           <t>C | 590呎 (3房)
 $1405万
 $23,814/呎
-(26年-04月)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
     </row>
@@ -39824,7 +39832,7 @@
           <t>A | 1339呎 (4+房)
 $5657万
 $42,248/呎
-(25年-08月)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -39832,7 +39840,7 @@
           <t>B | 1171呎 (4+房)
 $4790万
 $40,905/呎
-(26年-07月)</t>
+(26年-07月-19日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -39840,7 +39848,7 @@
           <t>C | 590呎 (3房)
 $1440万
 $24,410/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
     </row>
@@ -39855,7 +39863,7 @@
           <t>A | 1428呎 (4+房)
 $5614万
 $39,314/呎
-(23年-05月)</t>
+(23年-05月-28日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -39863,7 +39871,7 @@
           <t>B | 1171呎 (4+房)
 $4763万
 $40,675/呎
-(26年-06月)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -39871,7 +39879,7 @@
           <t>C | 590呎 (3房)
 $1422万
 $24,108/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
     </row>
@@ -39886,7 +39894,7 @@
           <t>A | 1339呎 (4+房)
 $5468万
 $40,833/呎
-(24年-12月)</t>
+(24年-12月-02日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -39894,7 +39902,7 @@
           <t>B | 1171呎 (4+房)
 $4711万
 $40,231/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -39902,7 +39910,7 @@
           <t>C | 590呎 (3房)
 $1416万
 $24,001/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
     </row>
@@ -39917,7 +39925,7 @@
           <t>A | 1339呎 (4+房)
 $5558万
 $41,509/呎
-(25年-10月)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -39925,7 +39933,7 @@
           <t>B | 1171呎 (4+房)
 $4510万
 $38,514/呎
-(25年-11月)</t>
+(25年-11月-02日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -39933,7 +39941,7 @@
           <t>C | 590呎 (3房)
 $1410万
 $23,893/呎
-(26年-03月)</t>
+(26年-03月-08日)</t>
         </is>
       </c>
     </row>
@@ -39948,7 +39956,7 @@
           <t>A | 1339呎 (4+房)
 $5546万
 $41,419/呎
-(25年-11月)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -39956,7 +39964,7 @@
           <t>B | 1171呎 (4+房)
 $4493万
 $38,369/呎
-(25年-12月)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -39964,7 +39972,7 @@
           <t>C | 590呎 (3房)
 $1407万
 $23,839/呎
-(26年-03月)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
     </row>
@@ -39979,7 +39987,7 @@
           <t>A | 1339呎 (4+房)
 $5365万
 $40,067/呎
-(25年-06月)</t>
+(25年-06月-11日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -39987,7 +39995,7 @@
           <t>B | 1171呎 (4+房)
 $4557万
 $38,915/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -39995,7 +40003,7 @@
           <t>C | 590呎 (3房)
 $1361万
 $23,072/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
     </row>
@@ -40010,7 +40018,7 @@
           <t>A | 1339呎 (4+房)
 $5432万
 $40,568/呎
-(25年-11月)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -40018,7 +40026,7 @@
           <t>B | 1171呎 (4+房)
 $4408万
 $37,643/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -40026,7 +40034,7 @@
           <t>C | 590呎 (3房)
 $1397万
 $23,678/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
     </row>
@@ -40041,7 +40049,7 @@
           <t>A | 1339呎 (4+房)
 $5393万
 $40,275/呎
-(25年-07月)</t>
+(25年-07月-29日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -40049,7 +40057,7 @@
           <t>B | 1171呎 (4+房)
 $4379万
 $37,395/呎
-(25年-10月)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -40057,7 +40065,7 @@
           <t>C | 590呎 (3房)
 $1349万
 $22,864/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
     </row>
@@ -40072,7 +40080,7 @@
           <t>A | 1339呎 (4+房)
 $5327万
 $39,783/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -40080,7 +40088,7 @@
           <t>B | 1171呎 (4+房)
 $4460万
 $38,087/呎
-(26年-02月)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -40088,7 +40096,7 @@
           <t>C | 590呎 (3房)
 $1324万
 $22,446/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
     </row>
@@ -40103,7 +40111,7 @@
           <t>A | 1339呎 (4+房)
 $5223万
 $39,007/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -40111,7 +40119,7 @@
           <t>B | 1171呎 (4+房)
 $4412万
 $37,677/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr"/>
@@ -40315,7 +40323,7 @@
           <t>B | 920呎 (3房)
 $3982万
 $43,283/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
     </row>
@@ -40338,7 +40346,7 @@
           <t>B | 920呎 (3房)
 $3889万
 $42,272/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
     </row>
@@ -40361,7 +40369,7 @@
           <t>B | 920呎 (3房)
 $3638万
 $39,543/呎
-(25年-11月)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
     </row>
@@ -40384,7 +40392,7 @@
           <t>B | 920呎 (3房)
 $3610万
 $39,239/呎
-(25年-12月)</t>
+(25年-12月-21日)</t>
         </is>
       </c>
     </row>
@@ -40407,7 +40415,7 @@
           <t>B | 920呎 (3房)
 $3454万
 $37,543/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
     </row>
@@ -40422,7 +40430,7 @@
           <t>A | 1076呎 (4+房)
 $4590万
 $42,658/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -40430,7 +40438,7 @@
           <t>B | 1002呎 (3房)
 $3390万
 $33,832/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -40453,7 +40461,7 @@
           <t>B | 1002呎 (3房)
 $3345万
 $33,383/呎
-(24年-06月)</t>
+(24年-06月-25日)</t>
         </is>
       </c>
     </row>
@@ -40468,7 +40476,7 @@
           <t>A | 1173呎 (4+房)
 $4111万
 $35,047/呎
-(25年-06月)</t>
+(25年-06月-03日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -40476,7 +40484,7 @@
           <t>B | 1002呎 (3房)
 $3310万
 $33,034/呎
-(24年-05月)</t>
+(24年-05月-01日)</t>
         </is>
       </c>
     </row>
@@ -40491,7 +40499,7 @@
           <t>A | 1076呎 (4+房)
 $4388万
 $40,781/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -40499,7 +40507,7 @@
           <t>B | 920呎 (3房)
 $3306万
 $35,935/呎
-(24年-06月)</t>
+(24年-06月-03日)</t>
         </is>
       </c>
     </row>
@@ -40514,7 +40522,7 @@
           <t>A | 1076呎 (4+房)
 $4365万
 $40,567/呎
-(26年-04月)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -40522,7 +40530,7 @@
           <t>B | 1002呎 (3房)
 $3286万
 $32,794/呎
-(24年-05月)</t>
+(24年-05月-09日)</t>
         </is>
       </c>
     </row>
@@ -40537,7 +40545,7 @@
           <t>A | 1173呎 (4+房)
 $4100万
 $34,953/呎
-(23年-05月)</t>
+(23年-05月-30日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -40545,7 +40553,7 @@
           <t>B | 1002呎 (3房)
 $3270万
 $32,635/呎
-(24年-07月)</t>
+(24年-07月-14日)</t>
         </is>
       </c>
     </row>
@@ -40560,7 +40568,7 @@
           <t>A | 1076呎 (4+房)
 $4038万
 $37,528/呎
-(25年-07月)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -40568,7 +40576,7 @@
           <t>B | 920呎 (3房)
 $3303万
 $35,902/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
     </row>
@@ -40583,7 +40591,7 @@
           <t>A | 1173呎 (4+房)
 $3990万
 $34,015/呎
-(24年-04月)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -40591,7 +40599,7 @@
           <t>B | 1002呎 (3房)
 $3228万
 $32,216/呎
-(24年-04月)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -40606,7 +40614,7 @@
           <t>A | 1173呎 (4+房)
 $3965万
 $33,802/呎
-(24年-03月)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -40614,7 +40622,7 @@
           <t>B | 1002呎 (3房)
 $3190万
 $31,836/呎
-(24年-04月)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
     </row>
@@ -40629,7 +40637,7 @@
           <t>A | 1173呎 (4+房)
 $3921万
 $33,427/呎
-(23年-11月)</t>
+(23年-11月-09日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -40637,7 +40645,7 @@
           <t>B | 1002呎 (3房)
 $3157万
 $31,507/呎
-(23年-05月)</t>
+(23年-05月-18日)</t>
         </is>
       </c>
     </row>
@@ -40652,7 +40660,7 @@
           <t>A | 1173呎 (4+房)
 $3997万
 $34,075/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -40660,7 +40668,7 @@
           <t>B | 920呎 (3房)
 $3140万
 $34,130/呎
-(24年-03月)</t>
+(24年-03月-24日)</t>
         </is>
       </c>
     </row>
@@ -40675,7 +40683,7 @@
           <t>A | 1173呎 (4+房)
 $3972万
 $33,862/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -40683,7 +40691,7 @@
           <t>B | 920呎 (3房)
 $3219万
 $34,989/呎
-(25年-08月)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
     </row>
@@ -40698,7 +40706,7 @@
           <t>A | 1173呎 (4+房)
 $3861万
 $32,917/呎
-(23年-11月)</t>
+(23年-11月-29日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -40706,7 +40714,7 @@
           <t>B | 1002呎 (3房)
 $3130万
 $31,238/呎
-(24年-05月)</t>
+(24年-05月-09日)</t>
         </is>
       </c>
     </row>
@@ -40721,7 +40729,7 @@
           <t>A | 1173呎 (4+房)
 $3910万
 $33,333/呎
-(23年-07月)</t>
+(23年-07月-19日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -40729,7 +40737,7 @@
           <t>B | 1002呎 (3房)
 $3093万
 $30,868/呎
-(24年-04月)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
     </row>
@@ -40744,7 +40752,7 @@
           <t>A | 1076呎 (4+房)
 $3836万
 $35,651/呎
-(24年-04月)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -40752,7 +40760,7 @@
           <t>B | 1002呎 (3房)
 $3103万
 $30,968/呎
-(24年-05月)</t>
+(24年-05月-02日)</t>
         </is>
       </c>
     </row>
@@ -40767,7 +40775,7 @@
           <t>A | 1173呎 (4+房)
 $3854万
 $32,856/呎
-(23年-06月)</t>
+(23年-06月-01日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -40775,7 +40783,7 @@
           <t>B | 920呎 (3房)
 $3138万
 $34,109/呎
-(25年-09月)</t>
+(25年-09月-03日)</t>
         </is>
       </c>
     </row>
@@ -40790,7 +40798,7 @@
           <t>A | 1173呎 (4+房)
 $3780万
 $32,225/呎
-(24年-05月)</t>
+(24年-05月-06日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -40798,7 +40806,7 @@
           <t>B | 920呎 (3房)
 $3044万
 $33,087/呎
-(24年-05月)</t>
+(24年-05月-06日)</t>
         </is>
       </c>
     </row>
@@ -40813,7 +40821,7 @@
           <t>A | 1076呎 (4+房)
 $3730万
 $34,667/呎
-(24年-06月)</t>
+(24年-06月-05日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -40821,7 +40829,7 @@
           <t>B | 920呎 (3房)
 $3032万
 $32,957/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -40836,7 +40844,7 @@
           <t>A | 1076呎 (4+房)
 $3715万
 $34,526/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -40844,7 +40852,7 @@
           <t>B | 920呎 (3房)
 $3028万
 $32,913/呎
-(25年-04月)</t>
+(25年-04月-01日)</t>
         </is>
       </c>
     </row>
@@ -40859,7 +40867,7 @@
           <t>A | 1076呎 (4+房)
 $3651万
 $33,931/呎
-(25年-05月)</t>
+(25年-05月-20日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -40867,7 +40875,7 @@
           <t>B | 1002呎 (3房)
 $2960万
 $29,541/呎
-(25年-03月)</t>
+(25年-03月-31日)</t>
         </is>
       </c>
     </row>
@@ -40948,22 +40956,22 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>62</t>
         </is>
       </c>
     </row>
@@ -41005,7 +41013,7 @@
           <t>A | 1677呎 (4+房)
 $9203万
 $54,880/呎
-(23年-06月)</t>
+(23年-06月-27日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -41149,20 +41157,20 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>A | 1102呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="22" t="inlineStr">
+招标单位
+-
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t>B | 1085呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(已定价未售)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -41193,7 +41201,7 @@
           <t>A | 1102呎 (3房)
 $4042万
 $36,679/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -41201,7 +41209,7 @@
           <t>B | 1085呎 (3房)
 $4002万
 $36,885/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -41240,7 +41248,7 @@
           <t>B | 994呎 (3房)
 $4060万
 $40,845/呎
-(25年-12月)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -41279,7 +41287,7 @@
           <t>B | 994呎 (3房)
 $3860万
 $38,833/呎
-(25年-01月)</t>
+(25年-01月-14日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -41310,7 +41318,7 @@
           <t>A | 1102呎 (3房)
 $3774万
 $34,247/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -41318,7 +41326,7 @@
           <t>B | 1085呎 (3房)
 $3774万
 $34,783/呎
-(24年-12月)</t>
+(24年-12月-02日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -41349,7 +41357,7 @@
           <t>A | 1102呎 (3房)
 $3708万
 $33,648/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -41357,7 +41365,7 @@
           <t>B | 994呎 (3房)
 $3752万
 $37,746/呎
-(25年-01月)</t>
+(25年-01月-09日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -41388,7 +41396,7 @@
           <t>A | 1027呎 (3房)
 $3680万
 $35,833/呎
-(24年-04月)</t>
+(24年-04月-28日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -41396,7 +41404,7 @@
           <t>B | 994呎 (3房)
 $3660万
 $36,821/呎
-(24年-04月)</t>
+(24年-04月-28日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -41427,7 +41435,7 @@
           <t>A | 1102呎 (3房)
 $3671万
 $33,312/呎
-(24年-12月)</t>
+(24年-12月-02日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -41435,7 +41443,7 @@
           <t>B | 1085呎 (3房)
 $3672万
 $33,843/呎
-(24年-12月)</t>
+(24年-12月-02日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -41466,7 +41474,7 @@
           <t>A | 1027呎 (3房)
 $4114万
 $40,057/呎
-(26年-04月)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -41474,7 +41482,7 @@
           <t>B | 994呎 (3房)
 $4960万
 $49,899/呎
-(26年-06月)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -41505,7 +41513,7 @@
           <t>A | 1102呎 (3房)
 $3700万
 $33,575/呎
-(24年-04月)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -41513,7 +41521,7 @@
           <t>B | 994呎 (3房)
 $3629万
 $36,509/呎
-(24年-12月)</t>
+(24年-12月-05日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -41544,7 +41552,7 @@
           <t>A | 1102呎 (3房)
 $3627万
 $32,913/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -41552,7 +41560,7 @@
           <t>B | 1085呎 (3房)
 $3627万
 $33,428/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -41583,7 +41591,7 @@
           <t>A | 1027呎 (3房)
 $3584万
 $34,898/呎
-(24年-12月)</t>
+(24年-12月-02日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -41591,7 +41599,7 @@
           <t>B | 1085呎 (3房)
 $3584万
 $33,032/呎
-(24年-12月)</t>
+(24年-12月-05日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -41622,7 +41630,7 @@
           <t>A | 1027呎 (3房)
 $3563万
 $34,693/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -41630,7 +41638,7 @@
           <t>B | 1085呎 (3房)
 $3562万
 $32,832/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -41661,7 +41669,7 @@
           <t>A | 1027呎 (3房)
 $3593万
 $34,985/呎
-(25年-09月)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -41669,7 +41677,7 @@
           <t>B | 994呎 (3房)
 $3540万
 $35,611/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -41700,7 +41708,7 @@
           <t>A | 1102呎 (3房)
 $3520万
 $31,942/呎
-(24年-12月)</t>
+(24年-12月-05日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -41708,7 +41716,7 @@
           <t>B | 1085呎 (3房)
 $3518万
 $32,426/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -41739,7 +41747,7 @@
           <t>A | 1102呎 (3房)
 $3497万
 $31,730/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -41747,7 +41755,7 @@
           <t>B | 1085呎 (3房)
 $3497万
 $32,228/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -41778,7 +41786,7 @@
           <t>A | 1027呎 (3房)
 $3880万
 $37,780/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -41786,7 +41794,7 @@
           <t>B | 994呎 (3房)
 $3555万
 $35,765/呎
-(24年-12月)</t>
+(24年-12月-03日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -41817,7 +41825,7 @@
           <t>A | 1102呎 (3房)
 $3454万
 $31,338/呎
-(24年-12月)</t>
+(24年-12月-02日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -41825,7 +41833,7 @@
           <t>B | 994呎 (3房)
 $3454万
 $34,744/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -41856,7 +41864,7 @@
           <t>A | 1102呎 (3房)
 $3464万
 $31,434/呎
-(24年-12月)</t>
+(24年-12月-05日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -41864,7 +41872,7 @@
           <t>B | 1085呎 (3房)
 $3524万
 $32,479/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -41895,7 +41903,7 @@
           <t>A | 1102呎 (3房)
 $3428万
 $31,107/呎
-(24年-12月)</t>
+(24年-12月-15日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -41903,7 +41911,7 @@
           <t>B | 1085呎 (3房)
 $3450万
 $31,797/呎
-(24年-12月)</t>
+(24年-12月-15日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -41934,7 +41942,7 @@
           <t>A | 1102呎 (3房)
 $3388万
 $30,744/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -41942,7 +41950,7 @@
           <t>B | 1085呎 (3房)
 $3388万
 $31,226/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -41973,7 +41981,7 @@
           <t>A | 1102呎 (3房)
 $3357万
 $30,463/呎
-(24年-12月)</t>
+(24年-12月-02日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -41981,7 +41989,7 @@
           <t>B | 994呎 (3房)
 $3351万
 $33,712/呎
-(24年-12月)</t>
+(24年-12月-05日)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -42012,7 +42020,7 @@
           <t>A | 1027呎 (3房)
 $3323万
 $32,356/呎
-(25年-04月)</t>
+(25年-04月-07日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -42020,7 +42028,7 @@
           <t>B | 1085呎 (3房)
 $3290万
 $30,323/呎
-(25年-02月)</t>
+(25年-02月-27日)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -42051,7 +42059,7 @@
           <t>A | 1102呎 (3房)
 $3258万
 $29,564/呎
-(24年-12月)</t>
+(24年-12月-15日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -42059,7 +42067,7 @@
           <t>B | 994呎 (3房)
 $3530万
 $35,513/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -42154,7 +42162,7 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -42169,7 +42177,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -42265,20 +42273,20 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>A | 1382呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
+招标单位
+-
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>B | 1382呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -42301,7 +42309,7 @@
           <t>B | 1282呎 (4+房)
 $6036万
 $47,083/呎
-(26年-07月)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
     </row>
@@ -42324,7 +42332,7 @@
           <t>B | 1282呎 (4+房)
 $5982万
 $46,661/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
     </row>
@@ -42339,7 +42347,7 @@
           <t>A | 1282呎 (4+房)
 $5591万
 $43,612/呎
-(25年-11月)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -42347,7 +42355,7 @@
           <t>B | 1382呎 (4+房)
 $5390万
 $39,001/呎
-(23年-06月)</t>
+(23年-06月-08日)</t>
         </is>
       </c>
     </row>
@@ -42362,7 +42370,7 @@
           <t>A | 1382呎 (4+房)
 $5373万
 $38,878/呎
-(25年-02月)</t>
+(25年-02月-19日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -42370,7 +42378,7 @@
           <t>B | 1382呎 (4+房)
 $5373万
 $38,878/呎
-(25年-02月)</t>
+(25年-02月-19日)</t>
         </is>
       </c>
     </row>
@@ -42393,7 +42401,7 @@
           <t>B | 1282呎 (4+房)
 $5432万
 $42,371/呎
-(25年-09月)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
     </row>
@@ -42408,7 +42416,7 @@
           <t>A | 1382呎 (4+房)
 $5380万
 $38,929/呎
-(23年-06月)</t>
+(23年-06月-07日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -42416,7 +42424,7 @@
           <t>B | 1382呎 (4+房)
 $5380万
 $38,929/呎
-(23年-06月)</t>
+(23年-06月-07日)</t>
         </is>
       </c>
     </row>
@@ -42431,7 +42439,7 @@
           <t>A | 1382呎 (4+房)
 $5227万
 $37,822/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -42439,7 +42447,7 @@
           <t>B | 1282呎 (4+房)
 $5226万
 $40,767/呎
-(24年-12月)</t>
+(24年-12月-10日)</t>
         </is>
       </c>
     </row>
@@ -42454,7 +42462,7 @@
           <t>A | 1282呎 (4+房)
 $5195万
 $40,523/呎
-(25年-05月)</t>
+(25年-05月-05日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -42462,7 +42470,7 @@
           <t>B | 1282呎 (4+房)
 $5195万
 $40,523/呎
-(25年-06月)</t>
+(25年-06月-05日)</t>
         </is>
       </c>
     </row>
@@ -42477,7 +42485,7 @@
           <t>A | 1382呎 (4+房)
 $5165万
 $37,370/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -42485,7 +42493,7 @@
           <t>B | 1382呎 (4+房)
 $5145万
 $37,229/呎
-(24年-04月)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
     </row>
@@ -42500,7 +42508,7 @@
           <t>A | 1282呎 (4+房)
 $5246万
 $40,919/呎
-(25年-11月)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -42508,7 +42516,7 @@
           <t>B | 1382呎 (4+房)
 $5134万
 $37,151/呎
-(24年-11月)</t>
+(24年-11月-20日)</t>
         </is>
       </c>
     </row>
@@ -42523,7 +42531,7 @@
           <t>A | 1282呎 (4+房)
 $5428万
 $42,340/呎
-(26年-02月)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -42531,7 +42539,7 @@
           <t>B | 1382呎 (4+房)
 $5134万
 $37,149/呎
-(24年-11月)</t>
+(24年-11月-25日)</t>
         </is>
       </c>
     </row>
@@ -42546,7 +42554,7 @@
           <t>A | 1382呎 (4+房)
 $5080万
 $36,758/呎
-(25年-06月)</t>
+(25年-06月-03日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -42554,7 +42562,7 @@
           <t>B | 1382呎 (4+房)
 $5080万
 $36,758/呎
-(25年-06月)</t>
+(25年-06月-03日)</t>
         </is>
       </c>
     </row>
@@ -42569,7 +42577,7 @@
           <t>A | 1382呎 (4+房)
 $5043万
 $36,491/呎
-(24年-04月)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -42577,7 +42585,7 @@
           <t>B | 1382呎 (4+房)
 $5042万
 $36,484/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
     </row>
@@ -42592,7 +42600,7 @@
           <t>A | 1282呎 (4+房)
 $5070万
 $39,548/呎
-(25年-08月)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -42600,7 +42608,7 @@
           <t>B | 1282呎 (4+房)
 $5070万
 $39,548/呎
-(25年-08月)</t>
+(25年-08月-31日)</t>
         </is>
       </c>
     </row>
@@ -42615,7 +42623,7 @@
           <t>A | 1282呎 (4+房)
 $4981万
 $38,853/呎
-(25年-04月)</t>
+(25年-04月-23日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -42623,7 +42631,7 @@
           <t>B | 1282呎 (4+房)
 $5060万
 $39,470/呎
-(25年-08月)</t>
+(25年-08月-10日)</t>
         </is>
       </c>
     </row>
@@ -42638,7 +42646,7 @@
           <t>A | 1282呎 (4+房)
 $5050万
 $39,392/呎
-(25年-11月)</t>
+(25年-11月-24日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -42646,7 +42654,7 @@
           <t>B | 1282呎 (4+房)
 $5050万
 $39,392/呎
-(25年-10月)</t>
+(25年-10月-12日)</t>
         </is>
       </c>
     </row>
@@ -42661,7 +42669,7 @@
           <t>A | 1282呎 (4+房)
 $4898万
 $38,206/呎
-(25年-05月)</t>
+(25年-05月-07日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -42669,7 +42677,7 @@
           <t>B | 1282呎 (4+房)
 $4898万
 $38,206/呎
-(25年-05月)</t>
+(25年-05月-07日)</t>
         </is>
       </c>
     </row>
@@ -42684,7 +42692,7 @@
           <t>A | 1282呎 (4+房)
 $4995万
 $38,963/呎
-(25年-10月)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -42692,7 +42700,7 @@
           <t>B | 1382呎 (4+房)
 $4888万
 $35,371/呎
-(24年-11月)</t>
+(24年-11月-27日)</t>
         </is>
       </c>
     </row>
@@ -42707,7 +42715,7 @@
           <t>A | 1282呎 (4+房)
 $4966万
 $38,736/呎
-(25年-10月)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -42715,7 +42723,7 @@
           <t>B | 1282呎 (4+房)
 $4966万
 $38,736/呎
-(25年-10月)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
     </row>
@@ -42730,7 +42738,7 @@
           <t>A | 1282呎 (4+房)
 $4908万
 $38,284/呎
-(25年-10月)</t>
+(25年-10月-29日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -42738,7 +42746,7 @@
           <t>B | 1282呎 (4+房)
 $4908万
 $38,284/呎
-(25年-10月)</t>
+(25年-10月-29日)</t>
         </is>
       </c>
     </row>
@@ -42753,7 +42761,7 @@
           <t>A | 1282呎 (4+房)
 $4814万
 $37,549/呎
-(25年-10月)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -42761,7 +42769,7 @@
           <t>B | 1282呎 (4+房)
 $4819万
 $37,590/呎
-(25年-11月)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -42776,7 +42784,7 @@
           <t>A | 1282呎 (4+房)
 $4845万
 $37,793/呎
-(25年-11月)</t>
+(25年-11月-24日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -42784,7 +42792,7 @@
           <t>B | 1282呎 (4+房)
 $4961万
 $38,697/呎
-(25年-12月)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
     </row>
@@ -42799,7 +42807,7 @@
           <t>A | 1282呎 (4+房)
 $4882万
 $38,081/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -42807,7 +42815,7 @@
           <t>B | 1282呎 (4+房)
 $4753万
 $37,075/呎
-(25年-11月)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
     </row>
@@ -42822,7 +42830,7 @@
           <t>A | 1282呎 (4+房)
 $4868万
 $37,972/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -42830,7 +42838,7 @@
           <t>B | 1282呎 (4+房)
 $4877万
 $38,042/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
     </row>
@@ -42911,7 +42919,7 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -42926,7 +42934,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>64</t>
         </is>
       </c>
     </row>
@@ -43195,7 +43203,7 @@
           <t>A | 992呎 (3房)
 $4469万
 $45,050/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -43203,7 +43211,7 @@
           <t>B | 1027呎 (3房)
 $4518万
 $43,992/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -43234,7 +43242,7 @@
           <t>A | 992呎 (3房)
 $4405万
 $44,405/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -43273,7 +43281,7 @@
           <t>A | 992呎 (3房)
 $4341万
 $43,760/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -43281,7 +43289,7 @@
           <t>B | 1027呎 (3房)
 $4427万
 $43,106/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -43312,15 +43320,15 @@
           <t>A | 992呎 (3房)
 $4217万
 $42,510/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="C14" s="22" t="inlineStr">
+(26年-02月-24日)</t>
+        </is>
+      </c>
+      <c r="C14" s="25" t="inlineStr">
         <is>
           <t>B | 1102呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(已定价未售)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -43351,7 +43359,7 @@
           <t>A | 992呎 (3房)
 $3865万
 $38,962/呎
-(25年-09月)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -43359,7 +43367,7 @@
           <t>B | 1027呎 (3房)
 $4300万
 $41,870/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -43390,7 +43398,7 @@
           <t>A | 992呎 (3房)
 $3843万
 $38,740/呎
-(25年-10月)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -43398,7 +43406,7 @@
           <t>B | 1027呎 (3房)
 $3885万
 $37,829/呎
-(25年-10月)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -43429,7 +43437,7 @@
           <t>A | 992呎 (3房)
 $3898万
 $39,294/呎
-(25年-11月)</t>
+(25年-11月-24日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -43437,7 +43445,7 @@
           <t>B | 1027呎 (3房)
 $4129万
 $40,204/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -43468,7 +43476,7 @@
           <t>A | 992呎 (3房)
 $3820万
 $38,508/呎
-(25年-10月)</t>
+(25年-10月-12日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -43476,7 +43484,7 @@
           <t>B | 1027呎 (3房)
 $3935万
 $38,315/呎
-(25年-12月)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -43507,7 +43515,7 @@
           <t>A | 992呎 (3房)
 $3818万
 $38,488/呎
-(25年-11月)</t>
+(25年-11月-09日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -43515,7 +43523,7 @@
           <t>B | 1027呎 (3房)
 $3878万
 $37,760/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -43585,7 +43593,7 @@
           <t>A | 992呎 (3房)
 $3740万
 $37,702/呎
-(25年-10月)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -43593,7 +43601,7 @@
           <t>B | 1027呎 (3房)
 $3780万
 $36,806/呎
-(25年-09月)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -43624,7 +43632,7 @@
           <t>A | 992呎 (3房)
 $3730万
 $37,601/呎
-(25年-10月)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -43632,7 +43640,7 @@
           <t>B | 1027呎 (3房)
 $3700万
 $36,027/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -43663,7 +43671,7 @@
           <t>A | 992呎 (3房)
 $3679万
 $37,087/呎
-(25年-06月)</t>
+(25年-06月-26日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -43671,7 +43679,7 @@
           <t>B | 1027呎 (3房)
 $3728万
 $36,300/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -43702,7 +43710,7 @@
           <t>A | 992呎 (3房)
 $3600万
 $36,290/呎
-(25年-06月)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -43710,7 +43718,7 @@
           <t>B | 1027呎 (3房)
 $3640万
 $35,443/呎
-(25年-05月)</t>
+(25年-05月-05日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -43741,7 +43749,7 @@
           <t>A | 1085呎 (3房)
 $3587万
 $33,060/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -43749,7 +43757,7 @@
           <t>B | 1102呎 (3房)
 $3618万
 $32,831/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -43780,7 +43788,7 @@
           <t>A | 992呎 (3房)
 $3565万
 $35,938/呎
-(25年-04月)</t>
+(25年-04月-24日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -43788,7 +43796,7 @@
           <t>B | 1102呎 (3房)
 $3603万
 $32,695/呎
-(25年-05月)</t>
+(25年-05月-20日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -43819,7 +43827,7 @@
           <t>A | 992呎 (3房)
 $3626万
 $36,552/呎
-(25年-08月)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -43827,7 +43835,7 @@
           <t>B | 1027呎 (3房)
 $3664万
 $35,677/呎
-(25年-08月)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -43858,7 +43866,7 @@
           <t>A | 992呎 (3房)
 $3453万
 $34,808/呎
-(25年-05月)</t>
+(25年-05月-26日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -43866,7 +43874,7 @@
           <t>B | 1027呎 (3房)
 $3653万
 $35,570/呎
-(25年-09月)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -43897,7 +43905,7 @@
           <t>A | 992呎 (3房)
 $3274万
 $33,004/呎
-(25年-04月)</t>
+(25年-04月-07日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -43905,7 +43913,7 @@
           <t>B | 1042呎 (3房)
 $3771万
 $36,190/呎
-(26年-04月)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -43936,7 +43944,7 @@
           <t>A | 1085呎 (3房)
 $3230万
 $29,770/呎
-(25年-04月)</t>
+(25年-04月-16日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -43944,7 +43952,7 @@
           <t>B | 1042呎 (3房)
 $3193万
 $30,643/呎
-(25年-04月)</t>
+(25年-04月-16日)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -43975,15 +43983,15 @@
           <t>A | 992呎 (3房)
 $3184万
 $32,097/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="C31" s="22" t="inlineStr">
+(25年-04月-07日)</t>
+        </is>
+      </c>
+      <c r="C31" s="25" t="inlineStr">
         <is>
           <t>B | 1117呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(已定价未售)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -44014,7 +44022,7 @@
           <t>A | 1085呎 (3房)
 $3127万
 $28,820/呎
-(25年-05月)</t>
+(25年-05月-13日)</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">
@@ -44256,7 +44264,7 @@
           <t>A | 920呎 (3房)
 $4111万
 $44,685/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -44279,7 +44287,7 @@
           <t>A | 920呎 (3房)
 $3835万
 $41,685/呎
-(26年-01月)</t>
+(26年-01月-22日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -44287,7 +44295,7 @@
           <t>B | 1076呎 (4+房)
 $4636万
 $43,086/呎
-(26年-01月)</t>
+(26年-01月-22日)</t>
         </is>
       </c>
     </row>
@@ -44302,7 +44310,7 @@
           <t>A | 920呎 (3房)
 $3675万
 $39,946/呎
-(25年-11月)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -44310,7 +44318,7 @@
           <t>B | 1076呎 (4+房)
 $4430万
 $41,171/呎
-(25年-11月)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
     </row>
@@ -44325,7 +44333,7 @@
           <t>A | 920呎 (3房)
 $3643万
 $39,598/呎
-(25年-10月)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -44333,7 +44341,7 @@
           <t>B | 1076呎 (4+房)
 $4405万
 $40,939/呎
-(25年-10月)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
     </row>
@@ -44348,7 +44356,7 @@
           <t>A | 1002呎 (3房)
 $3613万
 $36,058/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -44356,7 +44364,7 @@
           <t>B | 1173呎 (4+房)
 $4370万
 $37,255/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
     </row>
@@ -44371,7 +44379,7 @@
           <t>A | 920呎 (3房)
 $3580万
 $38,913/呎
-(25年-08月)</t>
+(25年-08月-05日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -44379,7 +44387,7 @@
           <t>B | 1076呎 (4+房)
 $4345万
 $40,381/呎
-(25年-08月)</t>
+(25年-08月-17日)</t>
         </is>
       </c>
     </row>
@@ -44394,7 +44402,7 @@
           <t>A | 920呎 (3房)
 $3534万
 $38,413/呎
-(25年-07月)</t>
+(25年-07月-23日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -44402,7 +44410,7 @@
           <t>B | 1076呎 (4+房)
 $4298万
 $39,944/呎
-(25年-11月)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
     </row>
@@ -44417,7 +44425,7 @@
           <t>A | 920呎 (3房)
 $3472万
 $37,739/呎
-(25年-06月)</t>
+(25年-06月-09日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -44425,7 +44433,7 @@
           <t>B | 1173呎 (4+房)
 $4214万
 $35,925/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
     </row>
@@ -44440,7 +44448,7 @@
           <t>A | 920呎 (3房)
 $3513万
 $38,185/呎
-(25年-08月)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -44448,7 +44456,7 @@
           <t>B | 1076呎 (4+房)
 $4246万
 $39,461/呎
-(25年-08月)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
     </row>
@@ -44463,7 +44471,7 @@
           <t>A | 920呎 (3房)
 $3498万
 $38,022/呎
-(25年-08月)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -44471,7 +44479,7 @@
           <t>B | 1076呎 (4+房)
 $4228万
 $39,294/呎
-(25年-07月)</t>
+(25年-07月-24日)</t>
         </is>
       </c>
     </row>
@@ -44486,7 +44494,7 @@
           <t>A | 920呎 (3房)
 $3421万
 $37,185/呎
-(25年-04月)</t>
+(25年-04月-14日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -44494,7 +44502,7 @@
           <t>B | 1173呎 (4+房)
 $4140万
 $35,294/呎
-(25年-01月)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
     </row>
@@ -44509,7 +44517,7 @@
           <t>A | 1002呎 (3房)
 $3395万
 $33,882/呎
-(25年-07月)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -44517,7 +44525,7 @@
           <t>B | 1076呎 (4+房)
 $4188万
 $38,922/呎
-(25年-10月)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
     </row>
@@ -44532,7 +44540,7 @@
           <t>A | 920呎 (3房)
 $3380万
 $36,739/呎
-(25年-06月)</t>
+(25年-06月-05日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -44540,7 +44548,7 @@
           <t>B | 1076呎 (4+房)
 $4090万
 $38,011/呎
-(25年-05月)</t>
+(25年-05月-27日)</t>
         </is>
       </c>
     </row>
@@ -44555,7 +44563,7 @@
           <t>A | 920呎 (3房)
 $3359万
 $36,511/呎
-(25年-04月)</t>
+(25年-04月-29日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -44563,7 +44571,7 @@
           <t>B | 1173呎 (4+房)
 $4066万
 $34,663/呎
-(24年-12月)</t>
+(24年-12月-03日)</t>
         </is>
       </c>
     </row>
@@ -44578,7 +44586,7 @@
           <t>A | 920呎 (3房)
 $3330万
 $36,196/呎
-(24年-12月)</t>
+(24年-12月-30日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -44586,7 +44594,7 @@
           <t>B | 1076呎 (4+房)
 $4037万
 $37,519/呎
-(25年-06月)</t>
+(25年-06月-04日)</t>
         </is>
       </c>
     </row>
@@ -44601,7 +44609,7 @@
           <t>A | 920呎 (3房)
 $3318万
 $36,065/呎
-(24年-12月)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -44609,7 +44617,7 @@
           <t>B | 1173呎 (4+房)
 $4016万
 $34,237/呎
-(25年-05月)</t>
+(25年-05月-15日)</t>
         </is>
       </c>
     </row>
@@ -44624,7 +44632,7 @@
           <t>A | 1002呎 (3房)
 $3290万
 $32,834/呎
-(25年-01月)</t>
+(25年-01月-15日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -44632,7 +44640,7 @@
           <t>B | 1076呎 (3房)
 $4087万
 $37,983/呎
-(25年-10月)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
     </row>
@@ -44647,7 +44655,7 @@
           <t>A | 920呎 (3房)
 $3271万
 $35,554/呎
-(25年-04月)</t>
+(25年-04月-29日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -44655,7 +44663,7 @@
           <t>B | 1076呎 (4+房)
 $3958万
 $36,784/呎
-(25年-06月)</t>
+(25年-06月-03日)</t>
         </is>
       </c>
     </row>
@@ -44670,7 +44678,7 @@
           <t>A | 920呎 (3房)
 $3295万
 $35,815/呎
-(25年-09月)</t>
+(25年-09月-03日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -44678,7 +44686,7 @@
           <t>B | 1076呎 (4+房)
 $3988万
 $37,063/呎
-(25年-10月)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
     </row>
@@ -44693,7 +44701,7 @@
           <t>A | 920呎 (3房)
 $3416万
 $37,130/呎
-(25年-12月)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -44701,7 +44709,7 @@
           <t>B | 1076呎 (4+房)
 $4058万
 $37,714/呎
-(26年-07月)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -44782,22 +44790,22 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>62</t>
         </is>
       </c>
     </row>
@@ -44839,7 +44847,7 @@
           <t>A | 1890呎 (4+房)
 $10395万
 $55,000/呎
-(23年-06月)</t>
+(23年-06月-07日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -45035,7 +45043,7 @@
           <t>B | 1298呎 (4+房)
 $5013万
 $38,621/呎
-(24年-04月)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -45066,7 +45074,7 @@
           <t>A | 1165呎 (4+房)
 $5381万
 $46,189/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -45113,7 +45121,7 @@
           <t>B | 1298呎 (4+房)
 $4936万
 $38,028/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -45144,7 +45152,7 @@
           <t>A | 1165呎 (4+房)
 $4898万
 $42,043/呎
-(25年-09月)</t>
+(25年-09月-21日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -45222,7 +45230,7 @@
           <t>A | 1259呎 (4+房)
 $4712万
 $37,426/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -45230,7 +45238,7 @@
           <t>B | 1298呎 (4+房)
 $4808万
 $37,042/呎
-(24年-05月)</t>
+(24年-05月-02日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -45261,7 +45269,7 @@
           <t>A | 1259呎 (4+房)
 $4663万
 $37,037/呎
-(24年-04月)</t>
+(24年-04月-28日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -45269,7 +45277,7 @@
           <t>B | 1298呎 (4+房)
 $4771万
 $36,757/呎
-(24年-04月)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -45300,7 +45308,7 @@
           <t>A | 1165呎 (4+房)
 $4988万
 $42,815/呎
-(26年-02月)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -45308,7 +45316,7 @@
           <t>B | 1204呎 (4+房)
 $5103万
 $42,384/呎
-(26年-02月)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -45347,7 +45355,7 @@
           <t>B | 1298呎 (4+房)
 $4765万
 $36,710/呎
-(24年-04月)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -45386,7 +45394,7 @@
           <t>B | 1298呎 (4+房)
 $4688万
 $36,117/呎
-(24年-04月)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -45417,7 +45425,7 @@
           <t>A | 1165呎 (4+房)
 $4800万
 $41,202/呎
-(26年-03月)</t>
+(26年-03月-22日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -45425,7 +45433,7 @@
           <t>B | 1298呎 (4+房)
 $4657万
 $35,878/呎
-(23年-06月)</t>
+(23年-06月-06日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -45495,7 +45503,7 @@
           <t>A | 1165呎 (4+房)
 $4750万
 $40,773/呎
-(26年-02月)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -45503,7 +45511,7 @@
           <t>B | 1204呎 (4+房)
 $5153万
 $42,799/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -45534,7 +45542,7 @@
           <t>A | 1165呎 (4+房)
 $4548万
 $39,039/呎
-(25年-09月)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -45542,7 +45550,7 @@
           <t>B | 1298呎 (4+房)
 $4646万
 $35,794/呎
-(25年-07月)</t>
+(25年-07月-21日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -45573,7 +45581,7 @@
           <t>A | 1165呎 (4+房)
 $4930万
 $42,318/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -45581,7 +45589,7 @@
           <t>B | 1204呎 (4+房)
 $4977万
 $41,337/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -45612,7 +45620,7 @@
           <t>A | 1165呎 (4+房)
 $4550万
 $39,056/呎
-(26年-02月)</t>
+(26年-02月-22日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -45620,7 +45628,7 @@
           <t>B | 1204呎 (4+房)
 $4900万
 $40,698/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -45651,7 +45659,7 @@
           <t>A | 1165呎 (4+房)
 $4520万
 $38,798/呎
-(26年-01月)</t>
+(26年-01月-26日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -45693,12 +45701,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C27" s="22" t="inlineStr">
+      <c r="C27" s="25" t="inlineStr">
         <is>
           <t>B | 1298呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(已定价未售)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -45724,12 +45732,12 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="25" t="inlineStr">
         <is>
           <t>A | 1259呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(已定价未售)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -45885,7 +45893,7 @@
           <t>A | 908呎 (3房)
 $3904万
 $43,000/呎
-(23年-06月)</t>
+(23年-06月-27日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -45902,7 +45910,7 @@
           <t>A | 900呎 (3房)
 $3199万
 $35,544/呎
-(23年-07月)</t>
+(23年-07月-31日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -45910,7 +45918,7 @@
           <t>B | 836呎 (3房)
 $2949万
 $35,280/呎
-(24年-03月)</t>
+(24年-03月-20日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -45918,7 +45926,7 @@
           <t>C | 907呎 (3房)
 $3127万
 $34,472/呎
-(24年-04月)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
     </row>
@@ -45933,7 +45941,7 @@
           <t>A | 900呎 (3房)
 $3397万
 $37,750/呎
-(23年-07月)</t>
+(23年-07月-17日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -45941,7 +45949,7 @@
           <t>B | 836呎 (3房)
 $2680万
 $32,060/呎
-(23年-07月)</t>
+(23年-07月-17日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -45949,7 +45957,7 @@
           <t>C | 907呎 (3房)
 $2916万
 $32,151/呎
-(23年-07月)</t>
+(23年-07月-17日)</t>
         </is>
       </c>
     </row>
